--- a/public/assets/templates/maintenance/electrical.xlsx
+++ b/public/assets/templates/maintenance/electrical.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ThinkPad\Documents\MAGANG\PT BAS\ENG\Maintenance\Template Laporan Form\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E507386-B4C8-4E2E-BF73-0A939816B63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1D4BC2-B3C1-42EF-9EEA-19C09024D76B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{1839BE4E-8ABA-4E0E-BDE7-D891D69ECECB}"/>
   </bookViews>
@@ -695,40 +695,289 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -738,254 +987,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1357,732 +1366,732 @@
   <dimension ref="A1:J69"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" style="95" customWidth="1"/>
-    <col min="2" max="2" width="3" style="95" customWidth="1"/>
-    <col min="3" max="3" width="23" style="95" customWidth="1"/>
-    <col min="4" max="4" width="6.26953125" style="95" customWidth="1"/>
-    <col min="5" max="5" width="2.26953125" style="95" customWidth="1"/>
-    <col min="6" max="6" width="15.26953125" style="95" customWidth="1"/>
-    <col min="7" max="7" width="4.7265625" style="95" customWidth="1"/>
-    <col min="8" max="8" width="6" style="95" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" style="27" customWidth="1"/>
+    <col min="2" max="2" width="3" style="27" customWidth="1"/>
+    <col min="3" max="3" width="23" style="27" customWidth="1"/>
+    <col min="4" max="4" width="6.26953125" style="27" customWidth="1"/>
+    <col min="5" max="5" width="2.26953125" style="27" customWidth="1"/>
+    <col min="6" max="6" width="15.26953125" style="27" customWidth="1"/>
+    <col min="7" max="7" width="4.7265625" style="27" customWidth="1"/>
+    <col min="8" max="8" width="6" style="27" customWidth="1"/>
     <col min="12" max="12" width="10.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" thickTop="1">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3" t="s">
+      <c r="A1" s="86"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="4"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90"/>
+      <c r="H1" s="91"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="5"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="7" t="s">
+      <c r="A2" s="88"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="92" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="8"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="93"/>
     </row>
     <row r="3" spans="1:8" ht="10.25" customHeight="1">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="11" t="s">
+      <c r="C3" s="2"/>
+      <c r="D3" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="11"/>
-      <c r="F3" s="12" t="s">
+      <c r="E3" s="94"/>
+      <c r="F3" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="12"/>
-      <c r="H3" s="13"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="96"/>
     </row>
     <row r="4" spans="1:8" ht="10.25" customHeight="1">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11" t="s">
+      <c r="C4" s="2"/>
+      <c r="D4" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="12" t="s">
+      <c r="E4" s="94"/>
+      <c r="F4" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="12"/>
-      <c r="H4" s="13"/>
-    </row>
-    <row r="5" spans="1:8" s="20" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A5" s="14" t="s">
+      <c r="G4" s="95"/>
+      <c r="H4" s="96"/>
+    </row>
+    <row r="5" spans="1:8" s="5" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="16" t="s">
+      <c r="C5" s="83"/>
+      <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="19"/>
-    </row>
-    <row r="6" spans="1:8" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A6" s="21" t="s">
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="85"/>
+    </row>
+    <row r="6" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A6" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="23" t="s">
+      <c r="B6" s="6"/>
+      <c r="C6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="26"/>
-    </row>
-    <row r="7" spans="1:8" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A7" s="28"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="29" t="s">
+      <c r="D6" s="97"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="77"/>
+      <c r="H6" s="78"/>
+    </row>
+    <row r="7" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A7" s="81"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="26"/>
-    </row>
-    <row r="8" spans="1:8" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A8" s="28"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="23" t="s">
+      <c r="D7" s="97"/>
+      <c r="E7" s="76"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="78"/>
+    </row>
+    <row r="8" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A8" s="81"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="22"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="26"/>
-    </row>
-    <row r="9" spans="1:8" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A9" s="28"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="23" t="s">
+      <c r="D8" s="97"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="78"/>
+    </row>
+    <row r="9" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A9" s="81"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="22"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="26"/>
-    </row>
-    <row r="10" spans="1:8" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A10" s="28"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="23" t="s">
+      <c r="D9" s="97"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="78"/>
+    </row>
+    <row r="10" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A10" s="81"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="26"/>
-    </row>
-    <row r="11" spans="1:8" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A11" s="28"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="23" t="s">
+      <c r="D10" s="97"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="78"/>
+    </row>
+    <row r="11" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A11" s="81"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="26"/>
-    </row>
-    <row r="12" spans="1:8" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A12" s="28"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="23" t="s">
+      <c r="D11" s="97"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="78"/>
+    </row>
+    <row r="12" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A12" s="81"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="22"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="26"/>
-    </row>
-    <row r="13" spans="1:8" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A13" s="28"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="23" t="s">
+      <c r="D12" s="97"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="78"/>
+    </row>
+    <row r="13" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A13" s="81"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="22"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="26"/>
-    </row>
-    <row r="14" spans="1:8" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A14" s="28"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="30" t="s">
+      <c r="D13" s="97"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="78"/>
+    </row>
+    <row r="14" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A14" s="81"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="26"/>
-    </row>
-    <row r="15" spans="1:8" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A15" s="28"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="23" t="s">
+      <c r="D14" s="97"/>
+      <c r="E14" s="76"/>
+      <c r="F14" s="77"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="78"/>
+    </row>
+    <row r="15" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A15" s="81"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="22"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="26"/>
-    </row>
-    <row r="16" spans="1:8" s="30" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A16" s="31"/>
-      <c r="B16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="26"/>
-    </row>
-    <row r="17" spans="1:10" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A17" s="21" t="s">
+      <c r="D15" s="97"/>
+      <c r="E15" s="76"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="78"/>
+    </row>
+    <row r="16" spans="1:8" s="10" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A16" s="82"/>
+      <c r="B16" s="6"/>
+      <c r="D16" s="97"/>
+      <c r="E16" s="76"/>
+      <c r="F16" s="77"/>
+      <c r="G16" s="77"/>
+      <c r="H16" s="78"/>
+    </row>
+    <row r="17" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A17" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="23" t="s">
+      <c r="B17" s="6"/>
+      <c r="C17" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="22"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="26"/>
-    </row>
-    <row r="18" spans="1:10" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A18" s="28"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="23" t="s">
+      <c r="D17" s="97"/>
+      <c r="E17" s="76"/>
+      <c r="F17" s="77"/>
+      <c r="G17" s="77"/>
+      <c r="H17" s="78"/>
+    </row>
+    <row r="18" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A18" s="81"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="22"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="26"/>
-    </row>
-    <row r="19" spans="1:10" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A19" s="28"/>
-      <c r="B19" s="22"/>
-      <c r="C19" s="23" t="s">
+      <c r="D18" s="97"/>
+      <c r="E18" s="76"/>
+      <c r="F18" s="77"/>
+      <c r="G18" s="77"/>
+      <c r="H18" s="78"/>
+    </row>
+    <row r="19" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A19" s="81"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="22"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="26"/>
-    </row>
-    <row r="20" spans="1:10" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A20" s="28"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="32" t="s">
+      <c r="D19" s="97"/>
+      <c r="E19" s="76"/>
+      <c r="F19" s="77"/>
+      <c r="G19" s="77"/>
+      <c r="H19" s="78"/>
+    </row>
+    <row r="20" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A20" s="81"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="22"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="26"/>
-    </row>
-    <row r="21" spans="1:10" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A21" s="28"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="33" t="s">
+      <c r="D20" s="97"/>
+      <c r="E20" s="76"/>
+      <c r="F20" s="77"/>
+      <c r="G20" s="77"/>
+      <c r="H20" s="78"/>
+    </row>
+    <row r="21" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A21" s="81"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="22"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="26"/>
-    </row>
-    <row r="22" spans="1:10" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A22" s="28"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="26"/>
-    </row>
-    <row r="23" spans="1:10" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A23" s="31"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="34"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="26"/>
-    </row>
-    <row r="24" spans="1:10" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A24" s="35" t="s">
+      <c r="D21" s="97"/>
+      <c r="E21" s="76"/>
+      <c r="F21" s="77"/>
+      <c r="G21" s="77"/>
+      <c r="H21" s="78"/>
+    </row>
+    <row r="22" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A22" s="81"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="97"/>
+      <c r="E22" s="76"/>
+      <c r="F22" s="77"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="78"/>
+    </row>
+    <row r="23" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A23" s="82"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="97"/>
+      <c r="E23" s="76"/>
+      <c r="F23" s="77"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="78"/>
+    </row>
+    <row r="24" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A24" s="79" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="22"/>
-      <c r="C24" s="23" t="s">
+      <c r="B24" s="6"/>
+      <c r="C24" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D24" s="22"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="26"/>
-    </row>
-    <row r="25" spans="1:10" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A25" s="35"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="36" t="s">
+      <c r="D24" s="97"/>
+      <c r="E24" s="76"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="78"/>
+    </row>
+    <row r="25" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A25" s="79"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D25" s="22"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="26"/>
-      <c r="J25" s="37"/>
-    </row>
-    <row r="26" spans="1:10" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A26" s="35"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="36" t="s">
+      <c r="D25" s="97"/>
+      <c r="E25" s="76"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="78"/>
+      <c r="J25" s="15"/>
+    </row>
+    <row r="26" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A26" s="79"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D26" s="22"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="26"/>
-    </row>
-    <row r="27" spans="1:10" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A27" s="35"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="36" t="s">
+      <c r="D26" s="97"/>
+      <c r="E26" s="76"/>
+      <c r="F26" s="77"/>
+      <c r="G26" s="77"/>
+      <c r="H26" s="78"/>
+    </row>
+    <row r="27" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A27" s="79"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D27" s="22"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="26"/>
-    </row>
-    <row r="28" spans="1:10" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A28" s="35"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="36" t="s">
+      <c r="D27" s="97"/>
+      <c r="E27" s="76"/>
+      <c r="F27" s="77"/>
+      <c r="G27" s="77"/>
+      <c r="H27" s="78"/>
+    </row>
+    <row r="28" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A28" s="79"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D28" s="22"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="26"/>
-    </row>
-    <row r="29" spans="1:10" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A29" s="35"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="36"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="26"/>
-    </row>
-    <row r="30" spans="1:10" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A30" s="35"/>
-      <c r="B30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="26"/>
-    </row>
-    <row r="31" spans="1:10" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A31" s="38" t="s">
+      <c r="D28" s="97"/>
+      <c r="E28" s="76"/>
+      <c r="F28" s="77"/>
+      <c r="G28" s="77"/>
+      <c r="H28" s="78"/>
+    </row>
+    <row r="29" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A29" s="79"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="97"/>
+      <c r="E29" s="76"/>
+      <c r="F29" s="77"/>
+      <c r="G29" s="77"/>
+      <c r="H29" s="78"/>
+    </row>
+    <row r="30" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A30" s="79"/>
+      <c r="B30" s="6"/>
+      <c r="D30" s="97"/>
+      <c r="E30" s="76"/>
+      <c r="F30" s="77"/>
+      <c r="G30" s="77"/>
+      <c r="H30" s="78"/>
+    </row>
+    <row r="31" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A31" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="22"/>
-      <c r="C31" s="39" t="s">
+      <c r="B31" s="6"/>
+      <c r="C31" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D31" s="22"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="26"/>
-    </row>
-    <row r="32" spans="1:10" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A32" s="40"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="39" t="s">
+      <c r="D31" s="97"/>
+      <c r="E31" s="76"/>
+      <c r="F31" s="77"/>
+      <c r="G31" s="77"/>
+      <c r="H31" s="78"/>
+    </row>
+    <row r="32" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A32" s="74"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D32" s="22"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="26"/>
-    </row>
-    <row r="33" spans="1:8" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A33" s="40"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="23" t="s">
+      <c r="D32" s="97"/>
+      <c r="E32" s="76"/>
+      <c r="F32" s="77"/>
+      <c r="G32" s="77"/>
+      <c r="H32" s="78"/>
+    </row>
+    <row r="33" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A33" s="74"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D33" s="22"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="26"/>
-    </row>
-    <row r="34" spans="1:8" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A34" s="40"/>
-      <c r="B34" s="22"/>
-      <c r="C34" s="23" t="s">
+      <c r="D33" s="97"/>
+      <c r="E33" s="76"/>
+      <c r="F33" s="77"/>
+      <c r="G33" s="77"/>
+      <c r="H33" s="78"/>
+    </row>
+    <row r="34" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A34" s="74"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="22"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="26"/>
-    </row>
-    <row r="35" spans="1:8" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A35" s="40"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="23"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="26"/>
-    </row>
-    <row r="36" spans="1:8" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A36" s="41"/>
-      <c r="B36" s="22"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="26"/>
-    </row>
-    <row r="37" spans="1:8" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A37" s="38" t="s">
+      <c r="D34" s="97"/>
+      <c r="E34" s="76"/>
+      <c r="F34" s="77"/>
+      <c r="G34" s="77"/>
+      <c r="H34" s="78"/>
+    </row>
+    <row r="35" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A35" s="74"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="97"/>
+      <c r="E35" s="76"/>
+      <c r="F35" s="77"/>
+      <c r="G35" s="77"/>
+      <c r="H35" s="78"/>
+    </row>
+    <row r="36" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A36" s="75"/>
+      <c r="B36" s="6"/>
+      <c r="D36" s="97"/>
+      <c r="E36" s="76"/>
+      <c r="F36" s="77"/>
+      <c r="G36" s="77"/>
+      <c r="H36" s="78"/>
+    </row>
+    <row r="37" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A37" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="22"/>
-      <c r="C37" s="23" t="s">
+      <c r="B37" s="6"/>
+      <c r="C37" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D37" s="22"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
-      <c r="H37" s="26"/>
-    </row>
-    <row r="38" spans="1:8" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A38" s="40"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="23" t="s">
+      <c r="D37" s="97"/>
+      <c r="E37" s="76"/>
+      <c r="F37" s="77"/>
+      <c r="G37" s="77"/>
+      <c r="H37" s="78"/>
+    </row>
+    <row r="38" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A38" s="74"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D38" s="22"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="26"/>
-    </row>
-    <row r="39" spans="1:8" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A39" s="40"/>
-      <c r="B39" s="22"/>
-      <c r="C39" s="42" t="s">
+      <c r="D38" s="97"/>
+      <c r="E38" s="76"/>
+      <c r="F38" s="77"/>
+      <c r="G38" s="77"/>
+      <c r="H38" s="78"/>
+    </row>
+    <row r="39" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A39" s="74"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D39" s="22"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="26"/>
-    </row>
-    <row r="40" spans="1:8" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A40" s="40"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25"/>
-      <c r="H40" s="26"/>
-    </row>
-    <row r="41" spans="1:8" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A41" s="41"/>
-      <c r="B41" s="43"/>
-      <c r="D41" s="43"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="25"/>
-      <c r="G41" s="25"/>
-      <c r="H41" s="26"/>
-    </row>
-    <row r="42" spans="1:8" s="27" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A42" s="44"/>
-      <c r="B42" s="45"/>
-      <c r="C42" s="45"/>
-      <c r="D42" s="45"/>
-      <c r="E42" s="46"/>
-      <c r="F42" s="46"/>
-      <c r="G42" s="46"/>
-      <c r="H42" s="47"/>
+      <c r="D39" s="97"/>
+      <c r="E39" s="76"/>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="78"/>
+    </row>
+    <row r="40" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A40" s="74"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="97"/>
+      <c r="E40" s="76"/>
+      <c r="F40" s="77"/>
+      <c r="G40" s="77"/>
+      <c r="H40" s="78"/>
+    </row>
+    <row r="41" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A41" s="75"/>
+      <c r="B41" s="18"/>
+      <c r="D41" s="98"/>
+      <c r="E41" s="76"/>
+      <c r="F41" s="77"/>
+      <c r="G41" s="77"/>
+      <c r="H41" s="78"/>
+    </row>
+    <row r="42" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A42" s="65"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="99"/>
+      <c r="E42" s="67"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="67"/>
+      <c r="H42" s="68"/>
     </row>
     <row r="43" spans="1:8" ht="9" customHeight="1">
-      <c r="A43" s="48"/>
-      <c r="B43" s="49"/>
-      <c r="C43" s="49"/>
-      <c r="D43" s="50"/>
-      <c r="E43" s="51"/>
-      <c r="F43" s="51"/>
-      <c r="G43" s="51"/>
-      <c r="H43" s="52"/>
+      <c r="A43" s="66"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="69"/>
+      <c r="F43" s="69"/>
+      <c r="G43" s="69"/>
+      <c r="H43" s="70"/>
     </row>
     <row r="44" spans="1:8" ht="9" customHeight="1">
-      <c r="A44" s="48"/>
-      <c r="B44" s="49"/>
-      <c r="C44" s="49"/>
-      <c r="D44" s="50"/>
-      <c r="E44" s="51"/>
-      <c r="F44" s="51"/>
-      <c r="G44" s="51"/>
-      <c r="H44" s="52"/>
+      <c r="A44" s="66"/>
+      <c r="B44" s="20"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="69"/>
+      <c r="F44" s="69"/>
+      <c r="G44" s="69"/>
+      <c r="H44" s="70"/>
     </row>
     <row r="45" spans="1:8" ht="9" customHeight="1">
-      <c r="A45" s="48"/>
-      <c r="B45" s="49"/>
-      <c r="C45" s="49"/>
-      <c r="D45" s="53"/>
-      <c r="E45" s="54"/>
-      <c r="F45" s="54"/>
-      <c r="G45" s="54"/>
-      <c r="H45" s="55"/>
+      <c r="A45" s="66"/>
+      <c r="B45" s="20"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="71"/>
+      <c r="F45" s="71"/>
+      <c r="G45" s="71"/>
+      <c r="H45" s="72"/>
     </row>
     <row r="46" spans="1:8" ht="9" customHeight="1">
-      <c r="A46" s="48"/>
-      <c r="B46" s="56"/>
-      <c r="C46" s="56"/>
-      <c r="D46" s="53"/>
-      <c r="E46" s="54"/>
-      <c r="F46" s="54"/>
-      <c r="G46" s="54"/>
-      <c r="H46" s="55"/>
+      <c r="A46" s="66"/>
+      <c r="B46" s="23"/>
+      <c r="C46" s="23"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
+      <c r="G46" s="71"/>
+      <c r="H46" s="72"/>
     </row>
     <row r="47" spans="1:8" ht="9" customHeight="1">
-      <c r="A47" s="57" t="s">
+      <c r="A47" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="B47" s="58"/>
-      <c r="C47" s="59"/>
-      <c r="D47" s="60" t="s">
+      <c r="B47" s="45"/>
+      <c r="C47" s="46"/>
+      <c r="D47" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="E47" s="60"/>
-      <c r="F47" s="60"/>
-      <c r="G47" s="60"/>
-      <c r="H47" s="61"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="53"/>
+      <c r="G47" s="53"/>
+      <c r="H47" s="54"/>
     </row>
     <row r="48" spans="1:8" ht="9" customHeight="1">
-      <c r="A48" s="62"/>
-      <c r="B48" s="63"/>
-      <c r="C48" s="64"/>
-      <c r="D48" s="65" t="s">
+      <c r="A48" s="47"/>
+      <c r="B48" s="48"/>
+      <c r="C48" s="49"/>
+      <c r="D48" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="E48" s="18"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="66"/>
-      <c r="H48" s="67" t="s">
+      <c r="E48" s="55"/>
+      <c r="F48" s="55"/>
+      <c r="G48" s="56"/>
+      <c r="H48" s="25" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="9" customHeight="1">
-      <c r="A49" s="62"/>
-      <c r="B49" s="63"/>
-      <c r="C49" s="64"/>
-      <c r="D49" s="68"/>
-      <c r="E49" s="69"/>
-      <c r="F49" s="69"/>
-      <c r="G49" s="70"/>
-      <c r="H49" s="71"/>
+      <c r="A49" s="47"/>
+      <c r="B49" s="48"/>
+      <c r="C49" s="49"/>
+      <c r="D49" s="57"/>
+      <c r="E49" s="58"/>
+      <c r="F49" s="58"/>
+      <c r="G49" s="59"/>
+      <c r="H49" s="26"/>
     </row>
     <row r="50" spans="1:8" ht="9" customHeight="1">
-      <c r="A50" s="62"/>
-      <c r="B50" s="63"/>
-      <c r="C50" s="64"/>
-      <c r="D50" s="68"/>
-      <c r="E50" s="69"/>
-      <c r="F50" s="69"/>
-      <c r="G50" s="70"/>
-      <c r="H50" s="71"/>
+      <c r="A50" s="47"/>
+      <c r="B50" s="48"/>
+      <c r="C50" s="49"/>
+      <c r="D50" s="57"/>
+      <c r="E50" s="58"/>
+      <c r="F50" s="58"/>
+      <c r="G50" s="59"/>
+      <c r="H50" s="26"/>
     </row>
     <row r="51" spans="1:8" ht="9" customHeight="1">
-      <c r="A51" s="62"/>
-      <c r="B51" s="63"/>
-      <c r="C51" s="64"/>
-      <c r="D51" s="68"/>
-      <c r="E51" s="69"/>
-      <c r="F51" s="69"/>
-      <c r="G51" s="70"/>
-      <c r="H51" s="71"/>
+      <c r="A51" s="47"/>
+      <c r="B51" s="48"/>
+      <c r="C51" s="49"/>
+      <c r="D51" s="57"/>
+      <c r="E51" s="58"/>
+      <c r="F51" s="58"/>
+      <c r="G51" s="59"/>
+      <c r="H51" s="26"/>
     </row>
     <row r="52" spans="1:8" ht="9" customHeight="1">
-      <c r="A52" s="62"/>
-      <c r="B52" s="63"/>
-      <c r="C52" s="64"/>
-      <c r="D52" s="68"/>
-      <c r="E52" s="69"/>
-      <c r="F52" s="69"/>
-      <c r="G52" s="70"/>
-      <c r="H52" s="71"/>
+      <c r="A52" s="47"/>
+      <c r="B52" s="48"/>
+      <c r="C52" s="49"/>
+      <c r="D52" s="57"/>
+      <c r="E52" s="58"/>
+      <c r="F52" s="58"/>
+      <c r="G52" s="59"/>
+      <c r="H52" s="26"/>
     </row>
     <row r="53" spans="1:8" ht="9" customHeight="1">
-      <c r="A53" s="62"/>
-      <c r="B53" s="63"/>
-      <c r="C53" s="64"/>
-      <c r="D53" s="68"/>
-      <c r="E53" s="69"/>
-      <c r="F53" s="69"/>
-      <c r="G53" s="70"/>
-      <c r="H53" s="71"/>
+      <c r="A53" s="47"/>
+      <c r="B53" s="48"/>
+      <c r="C53" s="49"/>
+      <c r="D53" s="57"/>
+      <c r="E53" s="58"/>
+      <c r="F53" s="58"/>
+      <c r="G53" s="59"/>
+      <c r="H53" s="26"/>
     </row>
     <row r="54" spans="1:8" ht="9" customHeight="1">
-      <c r="A54" s="62"/>
-      <c r="B54" s="63"/>
-      <c r="C54" s="64"/>
-      <c r="D54" s="72"/>
-      <c r="E54" s="73"/>
-      <c r="F54" s="73"/>
-      <c r="G54" s="70"/>
-      <c r="H54" s="71"/>
+      <c r="A54" s="47"/>
+      <c r="B54" s="48"/>
+      <c r="C54" s="49"/>
+      <c r="D54" s="60"/>
+      <c r="E54" s="61"/>
+      <c r="F54" s="61"/>
+      <c r="G54" s="59"/>
+      <c r="H54" s="26"/>
     </row>
     <row r="55" spans="1:8" ht="9" customHeight="1">
-      <c r="A55" s="62"/>
-      <c r="B55" s="63"/>
-      <c r="C55" s="64"/>
-      <c r="D55" s="74" t="s">
+      <c r="A55" s="47"/>
+      <c r="B55" s="48"/>
+      <c r="C55" s="49"/>
+      <c r="D55" s="62" t="s">
         <v>48</v>
       </c>
-      <c r="E55" s="75"/>
-      <c r="F55" s="76"/>
-      <c r="G55" s="77"/>
-      <c r="H55" s="78"/>
+      <c r="E55" s="63"/>
+      <c r="F55" s="64"/>
+      <c r="G55" s="29"/>
+      <c r="H55" s="30"/>
     </row>
     <row r="56" spans="1:8" ht="9" customHeight="1">
-      <c r="A56" s="62"/>
-      <c r="B56" s="63"/>
-      <c r="C56" s="64"/>
-      <c r="D56" s="79" t="s">
+      <c r="A56" s="47"/>
+      <c r="B56" s="48"/>
+      <c r="C56" s="49"/>
+      <c r="D56" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="E56" s="80"/>
-      <c r="F56" s="81"/>
-      <c r="G56" s="82"/>
-      <c r="H56" s="83"/>
+      <c r="E56" s="34"/>
+      <c r="F56" s="35"/>
+      <c r="G56" s="31"/>
+      <c r="H56" s="32"/>
     </row>
     <row r="57" spans="1:8" ht="9" customHeight="1">
-      <c r="A57" s="62"/>
-      <c r="B57" s="63"/>
-      <c r="C57" s="64"/>
-      <c r="D57" s="84" t="s">
+      <c r="A57" s="47"/>
+      <c r="B57" s="48"/>
+      <c r="C57" s="49"/>
+      <c r="D57" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="E57" s="85"/>
-      <c r="F57" s="86"/>
-      <c r="G57" s="77"/>
-      <c r="H57" s="78"/>
+      <c r="E57" s="37"/>
+      <c r="F57" s="38"/>
+      <c r="G57" s="29"/>
+      <c r="H57" s="30"/>
     </row>
     <row r="58" spans="1:8" ht="9" customHeight="1">
-      <c r="A58" s="62"/>
-      <c r="B58" s="63"/>
-      <c r="C58" s="64"/>
-      <c r="D58" s="79" t="s">
+      <c r="A58" s="47"/>
+      <c r="B58" s="48"/>
+      <c r="C58" s="49"/>
+      <c r="D58" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="E58" s="80"/>
-      <c r="F58" s="81"/>
-      <c r="G58" s="82"/>
-      <c r="H58" s="83"/>
+      <c r="E58" s="34"/>
+      <c r="F58" s="35"/>
+      <c r="G58" s="31"/>
+      <c r="H58" s="32"/>
     </row>
     <row r="59" spans="1:8" ht="9" customHeight="1">
-      <c r="A59" s="62"/>
-      <c r="B59" s="63"/>
-      <c r="C59" s="64"/>
-      <c r="D59" s="85" t="s">
+      <c r="A59" s="47"/>
+      <c r="B59" s="48"/>
+      <c r="C59" s="49"/>
+      <c r="D59" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="E59" s="85"/>
-      <c r="F59" s="86"/>
-      <c r="G59" s="77"/>
-      <c r="H59" s="78"/>
+      <c r="E59" s="37"/>
+      <c r="F59" s="38"/>
+      <c r="G59" s="29"/>
+      <c r="H59" s="30"/>
     </row>
     <row r="60" spans="1:8" ht="9" customHeight="1" thickBot="1">
-      <c r="A60" s="87"/>
-      <c r="B60" s="88"/>
-      <c r="C60" s="89"/>
-      <c r="D60" s="90" t="s">
+      <c r="A60" s="50"/>
+      <c r="B60" s="51"/>
+      <c r="C60" s="52"/>
+      <c r="D60" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="E60" s="91"/>
-      <c r="F60" s="92"/>
-      <c r="G60" s="93"/>
-      <c r="H60" s="94"/>
+      <c r="E60" s="42"/>
+      <c r="F60" s="43"/>
+      <c r="G60" s="39"/>
+      <c r="H60" s="40"/>
     </row>
     <row r="61" spans="1:8" ht="9" customHeight="1" thickTop="1">
-      <c r="F61" s="96" t="s">
+      <c r="F61" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="G61" s="96"/>
-      <c r="H61" s="96"/>
+      <c r="G61" s="28"/>
+      <c r="H61" s="28"/>
     </row>
     <row r="62" spans="1:8" ht="9" customHeight="1">
       <c r="A62"/>
@@ -2121,15 +2130,62 @@
     <row r="69" customFormat="1"/>
   </sheetData>
   <mergeCells count="75">
-    <mergeCell ref="F61:H61"/>
-    <mergeCell ref="G55:H56"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="G57:H58"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="G59:H60"/>
-    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="A6:A16"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="A24:A30"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="A31:A36"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="A37:A41"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="A42:A46"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:H46"/>
     <mergeCell ref="A47:C60"/>
     <mergeCell ref="D47:H47"/>
     <mergeCell ref="E48:G48"/>
@@ -2140,62 +2196,15 @@
     <mergeCell ref="D53:G53"/>
     <mergeCell ref="D54:G54"/>
     <mergeCell ref="D55:F55"/>
-    <mergeCell ref="A42:A46"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="A37:A41"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="A31:A36"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="A24:A30"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="A17:A23"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="A6:A16"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F61:H61"/>
+    <mergeCell ref="G55:H56"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="G57:H58"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="G59:H60"/>
+    <mergeCell ref="D60:F60"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.195138888888889" bottom="0" header="0" footer="0"/>

--- a/public/assets/templates/maintenance/electrical.xlsx
+++ b/public/assets/templates/maintenance/electrical.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1D4BC2-B3C1-42EF-9EEA-19C09024D76B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F99915-B410-4811-969B-9CC1EFE05CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{1839BE4E-8ABA-4E0E-BDE7-D891D69ECECB}"/>
   </bookViews>
@@ -33,10 +33,6 @@
     <t>PT BUMI ALAM SEGAR</t>
   </si>
   <si>
-    <t xml:space="preserve">Tanggal 
-</t>
-  </si>
-  <si>
     <t>:</t>
   </si>
   <si>
@@ -191,6 +187,9 @@
   </si>
   <si>
     <t>FRM/EUT/01/009/007-02</t>
+  </si>
+  <si>
+    <t>Tanggal</t>
   </si>
 </sst>
 </file>
@@ -780,6 +779,15 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -829,31 +837,31 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -954,6 +962,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -977,24 +994,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1378,720 +1377,720 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" thickTop="1">
-      <c r="A1" s="86"/>
-      <c r="B1" s="87"/>
-      <c r="C1" s="90" t="s">
+      <c r="A1" s="92"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
-      <c r="H1" s="91"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="97"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="88"/>
-      <c r="B2" s="89"/>
-      <c r="C2" s="92" t="s">
+      <c r="A2" s="94"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="98" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="93"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="99"/>
     </row>
     <row r="3" spans="1:8" ht="10.25" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2"/>
+      <c r="D3" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="94" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="94"/>
-      <c r="F3" s="95" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="95"/>
-      <c r="H3" s="96"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="90" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="90"/>
+      <c r="H3" s="91"/>
     </row>
     <row r="4" spans="1:8" ht="10.25" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="89" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="94" t="s">
+      <c r="E4" s="89"/>
+      <c r="F4" s="90" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="94"/>
-      <c r="F4" s="95" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="95"/>
-      <c r="H4" s="96"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="91"/>
     </row>
     <row r="5" spans="1:8" s="5" customFormat="1" ht="10.25" customHeight="1">
       <c r="A5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="83" t="s">
+      <c r="C5" s="86"/>
+      <c r="D5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="83"/>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="84" t="s">
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="88"/>
+    </row>
+    <row r="6" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A6" s="83" t="s">
         <v>11</v>
-      </c>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="85"/>
-    </row>
-    <row r="6" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A6" s="80" t="s">
-        <v>12</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="97"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77"/>
-      <c r="H6" s="78"/>
+        <v>12</v>
+      </c>
+      <c r="D6" s="28"/>
+      <c r="E6" s="79"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="81"/>
     </row>
     <row r="7" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A7" s="81"/>
+      <c r="A7" s="84"/>
       <c r="B7" s="6"/>
       <c r="C7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="97"/>
-      <c r="E7" s="76"/>
-      <c r="F7" s="77"/>
-      <c r="G7" s="77"/>
-      <c r="H7" s="78"/>
+        <v>13</v>
+      </c>
+      <c r="D7" s="28"/>
+      <c r="E7" s="79"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="81"/>
     </row>
     <row r="8" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A8" s="81"/>
+      <c r="A8" s="84"/>
       <c r="B8" s="6"/>
       <c r="C8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="97"/>
-      <c r="E8" s="76"/>
-      <c r="F8" s="77"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="78"/>
+        <v>14</v>
+      </c>
+      <c r="D8" s="28"/>
+      <c r="E8" s="79"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="81"/>
     </row>
     <row r="9" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A9" s="81"/>
+      <c r="A9" s="84"/>
       <c r="B9" s="6"/>
       <c r="C9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="97"/>
-      <c r="E9" s="76"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="78"/>
+        <v>15</v>
+      </c>
+      <c r="D9" s="28"/>
+      <c r="E9" s="79"/>
+      <c r="F9" s="80"/>
+      <c r="G9" s="80"/>
+      <c r="H9" s="81"/>
     </row>
     <row r="10" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A10" s="81"/>
+      <c r="A10" s="84"/>
       <c r="B10" s="6"/>
       <c r="C10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="97"/>
-      <c r="E10" s="76"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="78"/>
+        <v>16</v>
+      </c>
+      <c r="D10" s="28"/>
+      <c r="E10" s="79"/>
+      <c r="F10" s="80"/>
+      <c r="G10" s="80"/>
+      <c r="H10" s="81"/>
     </row>
     <row r="11" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A11" s="81"/>
+      <c r="A11" s="84"/>
       <c r="B11" s="6"/>
       <c r="C11" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="97"/>
-      <c r="E11" s="76"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="78"/>
+        <v>17</v>
+      </c>
+      <c r="D11" s="28"/>
+      <c r="E11" s="79"/>
+      <c r="F11" s="80"/>
+      <c r="G11" s="80"/>
+      <c r="H11" s="81"/>
     </row>
     <row r="12" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A12" s="81"/>
+      <c r="A12" s="84"/>
       <c r="B12" s="6"/>
       <c r="C12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="97"/>
-      <c r="E12" s="76"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="78"/>
+        <v>18</v>
+      </c>
+      <c r="D12" s="28"/>
+      <c r="E12" s="79"/>
+      <c r="F12" s="80"/>
+      <c r="G12" s="80"/>
+      <c r="H12" s="81"/>
     </row>
     <row r="13" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A13" s="81"/>
+      <c r="A13" s="84"/>
       <c r="B13" s="6"/>
       <c r="C13" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="97"/>
-      <c r="E13" s="76"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="78"/>
+        <v>19</v>
+      </c>
+      <c r="D13" s="28"/>
+      <c r="E13" s="79"/>
+      <c r="F13" s="80"/>
+      <c r="G13" s="80"/>
+      <c r="H13" s="81"/>
     </row>
     <row r="14" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A14" s="81"/>
+      <c r="A14" s="84"/>
       <c r="B14" s="6"/>
       <c r="C14" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="97"/>
-      <c r="E14" s="76"/>
-      <c r="F14" s="77"/>
-      <c r="G14" s="77"/>
-      <c r="H14" s="78"/>
+        <v>20</v>
+      </c>
+      <c r="D14" s="28"/>
+      <c r="E14" s="79"/>
+      <c r="F14" s="80"/>
+      <c r="G14" s="80"/>
+      <c r="H14" s="81"/>
     </row>
     <row r="15" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A15" s="81"/>
+      <c r="A15" s="84"/>
       <c r="B15" s="6"/>
       <c r="C15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="28"/>
+      <c r="E15" s="79"/>
+      <c r="F15" s="80"/>
+      <c r="G15" s="80"/>
+      <c r="H15" s="81"/>
+    </row>
+    <row r="16" spans="1:8" s="10" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A16" s="85"/>
+      <c r="B16" s="6"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="79"/>
+      <c r="F16" s="80"/>
+      <c r="G16" s="80"/>
+      <c r="H16" s="81"/>
+    </row>
+    <row r="17" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A17" s="83" t="s">
         <v>22</v>
-      </c>
-      <c r="D15" s="97"/>
-      <c r="E15" s="76"/>
-      <c r="F15" s="77"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="78"/>
-    </row>
-    <row r="16" spans="1:8" s="10" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A16" s="82"/>
-      <c r="B16" s="6"/>
-      <c r="D16" s="97"/>
-      <c r="E16" s="76"/>
-      <c r="F16" s="77"/>
-      <c r="G16" s="77"/>
-      <c r="H16" s="78"/>
-    </row>
-    <row r="17" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A17" s="80" t="s">
-        <v>23</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" s="97"/>
-      <c r="E17" s="76"/>
-      <c r="F17" s="77"/>
-      <c r="G17" s="77"/>
-      <c r="H17" s="78"/>
+        <v>23</v>
+      </c>
+      <c r="D17" s="28"/>
+      <c r="E17" s="79"/>
+      <c r="F17" s="80"/>
+      <c r="G17" s="80"/>
+      <c r="H17" s="81"/>
     </row>
     <row r="18" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A18" s="81"/>
+      <c r="A18" s="84"/>
       <c r="B18" s="6"/>
       <c r="C18" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="97"/>
-      <c r="E18" s="76"/>
-      <c r="F18" s="77"/>
-      <c r="G18" s="77"/>
-      <c r="H18" s="78"/>
+        <v>24</v>
+      </c>
+      <c r="D18" s="28"/>
+      <c r="E18" s="79"/>
+      <c r="F18" s="80"/>
+      <c r="G18" s="80"/>
+      <c r="H18" s="81"/>
     </row>
     <row r="19" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A19" s="81"/>
+      <c r="A19" s="84"/>
       <c r="B19" s="6"/>
       <c r="C19" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D19" s="97"/>
-      <c r="E19" s="76"/>
-      <c r="F19" s="77"/>
-      <c r="G19" s="77"/>
-      <c r="H19" s="78"/>
+        <v>25</v>
+      </c>
+      <c r="D19" s="28"/>
+      <c r="E19" s="79"/>
+      <c r="F19" s="80"/>
+      <c r="G19" s="80"/>
+      <c r="H19" s="81"/>
     </row>
     <row r="20" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A20" s="81"/>
+      <c r="A20" s="84"/>
       <c r="B20" s="6"/>
       <c r="C20" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D20" s="97"/>
-      <c r="E20" s="76"/>
-      <c r="F20" s="77"/>
-      <c r="G20" s="77"/>
-      <c r="H20" s="78"/>
+        <v>26</v>
+      </c>
+      <c r="D20" s="28"/>
+      <c r="E20" s="79"/>
+      <c r="F20" s="80"/>
+      <c r="G20" s="80"/>
+      <c r="H20" s="81"/>
     </row>
     <row r="21" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A21" s="81"/>
+      <c r="A21" s="84"/>
       <c r="B21" s="6"/>
       <c r="C21" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="97"/>
-      <c r="E21" s="76"/>
-      <c r="F21" s="77"/>
-      <c r="G21" s="77"/>
-      <c r="H21" s="78"/>
+        <v>27</v>
+      </c>
+      <c r="D21" s="28"/>
+      <c r="E21" s="79"/>
+      <c r="F21" s="80"/>
+      <c r="G21" s="80"/>
+      <c r="H21" s="81"/>
     </row>
     <row r="22" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A22" s="81"/>
+      <c r="A22" s="84"/>
       <c r="B22" s="6"/>
       <c r="C22" s="7"/>
-      <c r="D22" s="97"/>
-      <c r="E22" s="76"/>
-      <c r="F22" s="77"/>
-      <c r="G22" s="77"/>
-      <c r="H22" s="78"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="79"/>
+      <c r="F22" s="80"/>
+      <c r="G22" s="80"/>
+      <c r="H22" s="81"/>
     </row>
     <row r="23" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A23" s="82"/>
+      <c r="A23" s="85"/>
       <c r="B23" s="6"/>
       <c r="C23" s="13"/>
-      <c r="D23" s="97"/>
-      <c r="E23" s="76"/>
-      <c r="F23" s="77"/>
-      <c r="G23" s="77"/>
-      <c r="H23" s="78"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="79"/>
+      <c r="F23" s="80"/>
+      <c r="G23" s="80"/>
+      <c r="H23" s="81"/>
     </row>
     <row r="24" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A24" s="79" t="s">
-        <v>29</v>
+      <c r="A24" s="82" t="s">
+        <v>28</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D24" s="97"/>
-      <c r="E24" s="76"/>
-      <c r="F24" s="77"/>
-      <c r="G24" s="77"/>
-      <c r="H24" s="78"/>
+        <v>29</v>
+      </c>
+      <c r="D24" s="28"/>
+      <c r="E24" s="79"/>
+      <c r="F24" s="80"/>
+      <c r="G24" s="80"/>
+      <c r="H24" s="81"/>
     </row>
     <row r="25" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A25" s="79"/>
+      <c r="A25" s="82"/>
       <c r="B25" s="6"/>
       <c r="C25" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="D25" s="97"/>
-      <c r="E25" s="76"/>
-      <c r="F25" s="77"/>
-      <c r="G25" s="77"/>
-      <c r="H25" s="78"/>
+        <v>30</v>
+      </c>
+      <c r="D25" s="28"/>
+      <c r="E25" s="79"/>
+      <c r="F25" s="80"/>
+      <c r="G25" s="80"/>
+      <c r="H25" s="81"/>
       <c r="J25" s="15"/>
     </row>
     <row r="26" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A26" s="79"/>
+      <c r="A26" s="82"/>
       <c r="B26" s="6"/>
       <c r="C26" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D26" s="97"/>
-      <c r="E26" s="76"/>
-      <c r="F26" s="77"/>
-      <c r="G26" s="77"/>
-      <c r="H26" s="78"/>
+        <v>31</v>
+      </c>
+      <c r="D26" s="28"/>
+      <c r="E26" s="79"/>
+      <c r="F26" s="80"/>
+      <c r="G26" s="80"/>
+      <c r="H26" s="81"/>
     </row>
     <row r="27" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A27" s="79"/>
+      <c r="A27" s="82"/>
       <c r="B27" s="6"/>
       <c r="C27" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D27" s="97"/>
-      <c r="E27" s="76"/>
-      <c r="F27" s="77"/>
-      <c r="G27" s="77"/>
-      <c r="H27" s="78"/>
+        <v>32</v>
+      </c>
+      <c r="D27" s="28"/>
+      <c r="E27" s="79"/>
+      <c r="F27" s="80"/>
+      <c r="G27" s="80"/>
+      <c r="H27" s="81"/>
     </row>
     <row r="28" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A28" s="79"/>
+      <c r="A28" s="82"/>
       <c r="B28" s="6"/>
       <c r="C28" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D28" s="97"/>
-      <c r="E28" s="76"/>
-      <c r="F28" s="77"/>
-      <c r="G28" s="77"/>
-      <c r="H28" s="78"/>
+        <v>33</v>
+      </c>
+      <c r="D28" s="28"/>
+      <c r="E28" s="79"/>
+      <c r="F28" s="80"/>
+      <c r="G28" s="80"/>
+      <c r="H28" s="81"/>
     </row>
     <row r="29" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A29" s="79"/>
+      <c r="A29" s="82"/>
       <c r="B29" s="6"/>
       <c r="C29" s="14"/>
-      <c r="D29" s="97"/>
-      <c r="E29" s="76"/>
-      <c r="F29" s="77"/>
-      <c r="G29" s="77"/>
-      <c r="H29" s="78"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="79"/>
+      <c r="F29" s="80"/>
+      <c r="G29" s="80"/>
+      <c r="H29" s="81"/>
     </row>
     <row r="30" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A30" s="79"/>
+      <c r="A30" s="82"/>
       <c r="B30" s="6"/>
-      <c r="D30" s="97"/>
-      <c r="E30" s="76"/>
-      <c r="F30" s="77"/>
-      <c r="G30" s="77"/>
-      <c r="H30" s="78"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="79"/>
+      <c r="F30" s="80"/>
+      <c r="G30" s="80"/>
+      <c r="H30" s="81"/>
     </row>
     <row r="31" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A31" s="73" t="s">
-        <v>35</v>
+      <c r="A31" s="76" t="s">
+        <v>34</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="D31" s="97"/>
-      <c r="E31" s="76"/>
-      <c r="F31" s="77"/>
-      <c r="G31" s="77"/>
-      <c r="H31" s="78"/>
+        <v>35</v>
+      </c>
+      <c r="D31" s="28"/>
+      <c r="E31" s="79"/>
+      <c r="F31" s="80"/>
+      <c r="G31" s="80"/>
+      <c r="H31" s="81"/>
     </row>
     <row r="32" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A32" s="74"/>
+      <c r="A32" s="77"/>
       <c r="B32" s="6"/>
       <c r="C32" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="D32" s="97"/>
-      <c r="E32" s="76"/>
-      <c r="F32" s="77"/>
-      <c r="G32" s="77"/>
-      <c r="H32" s="78"/>
+        <v>36</v>
+      </c>
+      <c r="D32" s="28"/>
+      <c r="E32" s="79"/>
+      <c r="F32" s="80"/>
+      <c r="G32" s="80"/>
+      <c r="H32" s="81"/>
     </row>
     <row r="33" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A33" s="74"/>
+      <c r="A33" s="77"/>
       <c r="B33" s="6"/>
       <c r="C33" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D33" s="97"/>
-      <c r="E33" s="76"/>
-      <c r="F33" s="77"/>
-      <c r="G33" s="77"/>
-      <c r="H33" s="78"/>
+        <v>37</v>
+      </c>
+      <c r="D33" s="28"/>
+      <c r="E33" s="79"/>
+      <c r="F33" s="80"/>
+      <c r="G33" s="80"/>
+      <c r="H33" s="81"/>
     </row>
     <row r="34" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A34" s="74"/>
+      <c r="A34" s="77"/>
       <c r="B34" s="6"/>
       <c r="C34" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D34" s="97"/>
-      <c r="E34" s="76"/>
-      <c r="F34" s="77"/>
-      <c r="G34" s="77"/>
-      <c r="H34" s="78"/>
+        <v>38</v>
+      </c>
+      <c r="D34" s="28"/>
+      <c r="E34" s="79"/>
+      <c r="F34" s="80"/>
+      <c r="G34" s="80"/>
+      <c r="H34" s="81"/>
     </row>
     <row r="35" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A35" s="74"/>
+      <c r="A35" s="77"/>
       <c r="B35" s="6"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="97"/>
-      <c r="E35" s="76"/>
-      <c r="F35" s="77"/>
-      <c r="G35" s="77"/>
-      <c r="H35" s="78"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="79"/>
+      <c r="F35" s="80"/>
+      <c r="G35" s="80"/>
+      <c r="H35" s="81"/>
     </row>
     <row r="36" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A36" s="75"/>
+      <c r="A36" s="78"/>
       <c r="B36" s="6"/>
-      <c r="D36" s="97"/>
-      <c r="E36" s="76"/>
-      <c r="F36" s="77"/>
-      <c r="G36" s="77"/>
-      <c r="H36" s="78"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="79"/>
+      <c r="F36" s="80"/>
+      <c r="G36" s="80"/>
+      <c r="H36" s="81"/>
     </row>
     <row r="37" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A37" s="73" t="s">
-        <v>40</v>
+      <c r="A37" s="76" t="s">
+        <v>39</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D37" s="97"/>
-      <c r="E37" s="76"/>
-      <c r="F37" s="77"/>
-      <c r="G37" s="77"/>
-      <c r="H37" s="78"/>
+        <v>40</v>
+      </c>
+      <c r="D37" s="28"/>
+      <c r="E37" s="79"/>
+      <c r="F37" s="80"/>
+      <c r="G37" s="80"/>
+      <c r="H37" s="81"/>
     </row>
     <row r="38" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A38" s="74"/>
+      <c r="A38" s="77"/>
       <c r="B38" s="6"/>
       <c r="C38" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D38" s="97"/>
-      <c r="E38" s="76"/>
-      <c r="F38" s="77"/>
-      <c r="G38" s="77"/>
-      <c r="H38" s="78"/>
+        <v>41</v>
+      </c>
+      <c r="D38" s="28"/>
+      <c r="E38" s="79"/>
+      <c r="F38" s="80"/>
+      <c r="G38" s="80"/>
+      <c r="H38" s="81"/>
     </row>
     <row r="39" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A39" s="74"/>
+      <c r="A39" s="77"/>
       <c r="B39" s="6"/>
       <c r="C39" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="D39" s="97"/>
-      <c r="E39" s="76"/>
-      <c r="F39" s="77"/>
-      <c r="G39" s="77"/>
-      <c r="H39" s="78"/>
+        <v>42</v>
+      </c>
+      <c r="D39" s="28"/>
+      <c r="E39" s="79"/>
+      <c r="F39" s="80"/>
+      <c r="G39" s="80"/>
+      <c r="H39" s="81"/>
     </row>
     <row r="40" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A40" s="74"/>
+      <c r="A40" s="77"/>
       <c r="B40" s="6"/>
       <c r="C40" s="7"/>
-      <c r="D40" s="97"/>
-      <c r="E40" s="76"/>
-      <c r="F40" s="77"/>
-      <c r="G40" s="77"/>
-      <c r="H40" s="78"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="79"/>
+      <c r="F40" s="80"/>
+      <c r="G40" s="80"/>
+      <c r="H40" s="81"/>
     </row>
     <row r="41" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A41" s="75"/>
+      <c r="A41" s="78"/>
       <c r="B41" s="18"/>
-      <c r="D41" s="98"/>
-      <c r="E41" s="76"/>
-      <c r="F41" s="77"/>
-      <c r="G41" s="77"/>
-      <c r="H41" s="78"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="79"/>
+      <c r="F41" s="80"/>
+      <c r="G41" s="80"/>
+      <c r="H41" s="81"/>
     </row>
     <row r="42" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A42" s="65"/>
+      <c r="A42" s="68"/>
       <c r="B42" s="19"/>
       <c r="C42" s="19"/>
-      <c r="D42" s="99"/>
-      <c r="E42" s="67"/>
-      <c r="F42" s="67"/>
-      <c r="G42" s="67"/>
-      <c r="H42" s="68"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="71"/>
     </row>
     <row r="43" spans="1:8" ht="9" customHeight="1">
-      <c r="A43" s="66"/>
+      <c r="A43" s="69"/>
       <c r="B43" s="20"/>
       <c r="C43" s="20"/>
       <c r="D43" s="21"/>
-      <c r="E43" s="69"/>
-      <c r="F43" s="69"/>
-      <c r="G43" s="69"/>
-      <c r="H43" s="70"/>
+      <c r="E43" s="72"/>
+      <c r="F43" s="72"/>
+      <c r="G43" s="72"/>
+      <c r="H43" s="73"/>
     </row>
     <row r="44" spans="1:8" ht="9" customHeight="1">
-      <c r="A44" s="66"/>
+      <c r="A44" s="69"/>
       <c r="B44" s="20"/>
       <c r="C44" s="20"/>
       <c r="D44" s="21"/>
-      <c r="E44" s="69"/>
-      <c r="F44" s="69"/>
-      <c r="G44" s="69"/>
-      <c r="H44" s="70"/>
+      <c r="E44" s="72"/>
+      <c r="F44" s="72"/>
+      <c r="G44" s="72"/>
+      <c r="H44" s="73"/>
     </row>
     <row r="45" spans="1:8" ht="9" customHeight="1">
-      <c r="A45" s="66"/>
+      <c r="A45" s="69"/>
       <c r="B45" s="20"/>
       <c r="C45" s="20"/>
       <c r="D45" s="22"/>
-      <c r="E45" s="71"/>
-      <c r="F45" s="71"/>
-      <c r="G45" s="71"/>
-      <c r="H45" s="72"/>
+      <c r="E45" s="74"/>
+      <c r="F45" s="74"/>
+      <c r="G45" s="74"/>
+      <c r="H45" s="75"/>
     </row>
     <row r="46" spans="1:8" ht="9" customHeight="1">
-      <c r="A46" s="66"/>
+      <c r="A46" s="69"/>
       <c r="B46" s="23"/>
       <c r="C46" s="23"/>
       <c r="D46" s="22"/>
-      <c r="E46" s="71"/>
-      <c r="F46" s="71"/>
-      <c r="G46" s="71"/>
-      <c r="H46" s="72"/>
+      <c r="E46" s="74"/>
+      <c r="F46" s="74"/>
+      <c r="G46" s="74"/>
+      <c r="H46" s="75"/>
     </row>
     <row r="47" spans="1:8" ht="9" customHeight="1">
-      <c r="A47" s="44" t="s">
+      <c r="A47" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="B47" s="48"/>
+      <c r="C47" s="49"/>
+      <c r="D47" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B47" s="45"/>
-      <c r="C47" s="46"/>
-      <c r="D47" s="53" t="s">
+      <c r="E47" s="56"/>
+      <c r="F47" s="56"/>
+      <c r="G47" s="56"/>
+      <c r="H47" s="57"/>
+    </row>
+    <row r="48" spans="1:8" ht="9" customHeight="1">
+      <c r="A48" s="50"/>
+      <c r="B48" s="51"/>
+      <c r="C48" s="52"/>
+      <c r="D48" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E47" s="53"/>
-      <c r="F47" s="53"/>
-      <c r="G47" s="53"/>
-      <c r="H47" s="54"/>
-    </row>
-    <row r="48" spans="1:8" ht="9" customHeight="1">
-      <c r="A48" s="47"/>
-      <c r="B48" s="48"/>
-      <c r="C48" s="49"/>
-      <c r="D48" s="24" t="s">
+      <c r="E48" s="58"/>
+      <c r="F48" s="58"/>
+      <c r="G48" s="59"/>
+      <c r="H48" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="E48" s="55"/>
-      <c r="F48" s="55"/>
-      <c r="G48" s="56"/>
-      <c r="H48" s="25" t="s">
+    </row>
+    <row r="49" spans="1:8" ht="9" customHeight="1">
+      <c r="A49" s="50"/>
+      <c r="B49" s="51"/>
+      <c r="C49" s="52"/>
+      <c r="D49" s="60"/>
+      <c r="E49" s="61"/>
+      <c r="F49" s="61"/>
+      <c r="G49" s="62"/>
+      <c r="H49" s="26"/>
+    </row>
+    <row r="50" spans="1:8" ht="9" customHeight="1">
+      <c r="A50" s="50"/>
+      <c r="B50" s="51"/>
+      <c r="C50" s="52"/>
+      <c r="D50" s="60"/>
+      <c r="E50" s="61"/>
+      <c r="F50" s="61"/>
+      <c r="G50" s="62"/>
+      <c r="H50" s="26"/>
+    </row>
+    <row r="51" spans="1:8" ht="9" customHeight="1">
+      <c r="A51" s="50"/>
+      <c r="B51" s="51"/>
+      <c r="C51" s="52"/>
+      <c r="D51" s="60"/>
+      <c r="E51" s="61"/>
+      <c r="F51" s="61"/>
+      <c r="G51" s="62"/>
+      <c r="H51" s="26"/>
+    </row>
+    <row r="52" spans="1:8" ht="9" customHeight="1">
+      <c r="A52" s="50"/>
+      <c r="B52" s="51"/>
+      <c r="C52" s="52"/>
+      <c r="D52" s="60"/>
+      <c r="E52" s="61"/>
+      <c r="F52" s="61"/>
+      <c r="G52" s="62"/>
+      <c r="H52" s="26"/>
+    </row>
+    <row r="53" spans="1:8" ht="9" customHeight="1">
+      <c r="A53" s="50"/>
+      <c r="B53" s="51"/>
+      <c r="C53" s="52"/>
+      <c r="D53" s="60"/>
+      <c r="E53" s="61"/>
+      <c r="F53" s="61"/>
+      <c r="G53" s="62"/>
+      <c r="H53" s="26"/>
+    </row>
+    <row r="54" spans="1:8" ht="9" customHeight="1">
+      <c r="A54" s="50"/>
+      <c r="B54" s="51"/>
+      <c r="C54" s="52"/>
+      <c r="D54" s="63"/>
+      <c r="E54" s="64"/>
+      <c r="F54" s="64"/>
+      <c r="G54" s="62"/>
+      <c r="H54" s="26"/>
+    </row>
+    <row r="55" spans="1:8" ht="9" customHeight="1">
+      <c r="A55" s="50"/>
+      <c r="B55" s="51"/>
+      <c r="C55" s="52"/>
+      <c r="D55" s="65" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" ht="9" customHeight="1">
-      <c r="A49" s="47"/>
-      <c r="B49" s="48"/>
-      <c r="C49" s="49"/>
-      <c r="D49" s="57"/>
-      <c r="E49" s="58"/>
-      <c r="F49" s="58"/>
-      <c r="G49" s="59"/>
-      <c r="H49" s="26"/>
-    </row>
-    <row r="50" spans="1:8" ht="9" customHeight="1">
-      <c r="A50" s="47"/>
-      <c r="B50" s="48"/>
-      <c r="C50" s="49"/>
-      <c r="D50" s="57"/>
-      <c r="E50" s="58"/>
-      <c r="F50" s="58"/>
-      <c r="G50" s="59"/>
-      <c r="H50" s="26"/>
-    </row>
-    <row r="51" spans="1:8" ht="9" customHeight="1">
-      <c r="A51" s="47"/>
-      <c r="B51" s="48"/>
-      <c r="C51" s="49"/>
-      <c r="D51" s="57"/>
-      <c r="E51" s="58"/>
-      <c r="F51" s="58"/>
-      <c r="G51" s="59"/>
-      <c r="H51" s="26"/>
-    </row>
-    <row r="52" spans="1:8" ht="9" customHeight="1">
-      <c r="A52" s="47"/>
-      <c r="B52" s="48"/>
-      <c r="C52" s="49"/>
-      <c r="D52" s="57"/>
-      <c r="E52" s="58"/>
-      <c r="F52" s="58"/>
-      <c r="G52" s="59"/>
-      <c r="H52" s="26"/>
-    </row>
-    <row r="53" spans="1:8" ht="9" customHeight="1">
-      <c r="A53" s="47"/>
-      <c r="B53" s="48"/>
-      <c r="C53" s="49"/>
-      <c r="D53" s="57"/>
-      <c r="E53" s="58"/>
-      <c r="F53" s="58"/>
-      <c r="G53" s="59"/>
-      <c r="H53" s="26"/>
-    </row>
-    <row r="54" spans="1:8" ht="9" customHeight="1">
-      <c r="A54" s="47"/>
-      <c r="B54" s="48"/>
-      <c r="C54" s="49"/>
-      <c r="D54" s="60"/>
-      <c r="E54" s="61"/>
-      <c r="F54" s="61"/>
-      <c r="G54" s="59"/>
-      <c r="H54" s="26"/>
-    </row>
-    <row r="55" spans="1:8" ht="9" customHeight="1">
-      <c r="A55" s="47"/>
-      <c r="B55" s="48"/>
-      <c r="C55" s="49"/>
-      <c r="D55" s="62" t="s">
+      <c r="E55" s="66"/>
+      <c r="F55" s="67"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="33"/>
+    </row>
+    <row r="56" spans="1:8" ht="9" customHeight="1">
+      <c r="A56" s="50"/>
+      <c r="B56" s="51"/>
+      <c r="C56" s="52"/>
+      <c r="D56" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="E55" s="63"/>
-      <c r="F55" s="64"/>
-      <c r="G55" s="29"/>
-      <c r="H55" s="30"/>
-    </row>
-    <row r="56" spans="1:8" ht="9" customHeight="1">
-      <c r="A56" s="47"/>
-      <c r="B56" s="48"/>
-      <c r="C56" s="49"/>
-      <c r="D56" s="33" t="s">
+      <c r="E56" s="37"/>
+      <c r="F56" s="38"/>
+      <c r="G56" s="34"/>
+      <c r="H56" s="35"/>
+    </row>
+    <row r="57" spans="1:8" ht="9" customHeight="1">
+      <c r="A57" s="50"/>
+      <c r="B57" s="51"/>
+      <c r="C57" s="52"/>
+      <c r="D57" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="E56" s="34"/>
-      <c r="F56" s="35"/>
-      <c r="G56" s="31"/>
-      <c r="H56" s="32"/>
-    </row>
-    <row r="57" spans="1:8" ht="9" customHeight="1">
-      <c r="A57" s="47"/>
-      <c r="B57" s="48"/>
-      <c r="C57" s="49"/>
-      <c r="D57" s="36" t="s">
+      <c r="E57" s="40"/>
+      <c r="F57" s="41"/>
+      <c r="G57" s="32"/>
+      <c r="H57" s="33"/>
+    </row>
+    <row r="58" spans="1:8" ht="9" customHeight="1">
+      <c r="A58" s="50"/>
+      <c r="B58" s="51"/>
+      <c r="C58" s="52"/>
+      <c r="D58" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="E57" s="37"/>
-      <c r="F57" s="38"/>
-      <c r="G57" s="29"/>
-      <c r="H57" s="30"/>
-    </row>
-    <row r="58" spans="1:8" ht="9" customHeight="1">
-      <c r="A58" s="47"/>
-      <c r="B58" s="48"/>
-      <c r="C58" s="49"/>
-      <c r="D58" s="33" t="s">
+      <c r="E58" s="37"/>
+      <c r="F58" s="38"/>
+      <c r="G58" s="34"/>
+      <c r="H58" s="35"/>
+    </row>
+    <row r="59" spans="1:8" ht="9" customHeight="1">
+      <c r="A59" s="50"/>
+      <c r="B59" s="51"/>
+      <c r="C59" s="52"/>
+      <c r="D59" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="E58" s="34"/>
-      <c r="F58" s="35"/>
-      <c r="G58" s="31"/>
-      <c r="H58" s="32"/>
-    </row>
-    <row r="59" spans="1:8" ht="9" customHeight="1">
-      <c r="A59" s="47"/>
-      <c r="B59" s="48"/>
-      <c r="C59" s="49"/>
-      <c r="D59" s="37" t="s">
+      <c r="E59" s="40"/>
+      <c r="F59" s="41"/>
+      <c r="G59" s="32"/>
+      <c r="H59" s="33"/>
+    </row>
+    <row r="60" spans="1:8" ht="9" customHeight="1" thickBot="1">
+      <c r="A60" s="53"/>
+      <c r="B60" s="54"/>
+      <c r="C60" s="55"/>
+      <c r="D60" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="E59" s="37"/>
-      <c r="F59" s="38"/>
-      <c r="G59" s="29"/>
-      <c r="H59" s="30"/>
-    </row>
-    <row r="60" spans="1:8" ht="9" customHeight="1" thickBot="1">
-      <c r="A60" s="50"/>
-      <c r="B60" s="51"/>
-      <c r="C60" s="52"/>
-      <c r="D60" s="41" t="s">
+      <c r="E60" s="45"/>
+      <c r="F60" s="46"/>
+      <c r="G60" s="42"/>
+      <c r="H60" s="43"/>
+    </row>
+    <row r="61" spans="1:8" ht="9" customHeight="1" thickTop="1">
+      <c r="F61" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="E60" s="42"/>
-      <c r="F60" s="43"/>
-      <c r="G60" s="39"/>
-      <c r="H60" s="40"/>
-    </row>
-    <row r="61" spans="1:8" ht="9" customHeight="1" thickTop="1">
-      <c r="F61" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="G61" s="28"/>
-      <c r="H61" s="28"/>
+      <c r="G61" s="31"/>
+      <c r="H61" s="31"/>
     </row>
     <row r="62" spans="1:8" ht="9" customHeight="1">
       <c r="A62"/>

--- a/public/assets/templates/maintenance/electrical.xlsx
+++ b/public/assets/templates/maintenance/electrical.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F99915-B410-4811-969B-9CC1EFE05CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2D4D562-585D-497D-A19C-6947134E6EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{1839BE4E-8ABA-4E0E-BDE7-D891D69ECECB}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="59">
   <si>
     <t>LAPORAN MAINTENANCE ELECTRICAL</t>
   </si>
@@ -190,6 +190,18 @@
   </si>
   <si>
     <t>Tanggal</t>
+  </si>
+  <si>
+    <t>Waktu Mulai</t>
+  </si>
+  <si>
+    <t>Waktu Selesai</t>
+  </si>
+  <si>
+    <t>Kode Mesin</t>
+  </si>
+  <si>
+    <t>Lokasi</t>
   </si>
 </sst>
 </file>
@@ -788,6 +800,165 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -835,165 +1006,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1362,7 +1374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{493283BF-42BD-4599-A4C7-39F3C6173D54}">
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8.81640625" style="27" customWidth="1"/>
@@ -1377,28 +1389,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" thickTop="1">
-      <c r="A1" s="92"/>
-      <c r="B1" s="93"/>
-      <c r="C1" s="96" t="s">
+      <c r="A1" s="34"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="97"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="94"/>
-      <c r="B2" s="95"/>
-      <c r="C2" s="98" t="s">
+      <c r="A2" s="36"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="99"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="41"/>
     </row>
     <row r="3" spans="1:8" ht="10.25" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -1408,711 +1420,727 @@
         <v>2</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="89" t="s">
+      <c r="D3" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="89"/>
-      <c r="F3" s="90" t="s">
+      <c r="E3" s="31"/>
+      <c r="F3" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="90"/>
-      <c r="H3" s="91"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="33"/>
     </row>
     <row r="4" spans="1:8" ht="10.25" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="89" t="s">
+      <c r="D4" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="31"/>
+      <c r="F4" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="32"/>
+      <c r="H4" s="33"/>
+    </row>
+    <row r="5" spans="1:8" ht="10.25" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="31"/>
+      <c r="F5" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="G5" s="32"/>
+      <c r="H5" s="33"/>
+    </row>
+    <row r="6" spans="1:8" ht="10.25" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="89"/>
-      <c r="F4" s="90" t="s">
+      <c r="E6" s="31"/>
+      <c r="F6" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="90"/>
-      <c r="H4" s="91"/>
-    </row>
-    <row r="5" spans="1:8" s="5" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A5" s="3" t="s">
+      <c r="G6" s="32"/>
+      <c r="H6" s="33"/>
+    </row>
+    <row r="7" spans="1:8" s="5" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="86" t="s">
+      <c r="B7" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="86"/>
-      <c r="D5" s="4" t="s">
+      <c r="C7" s="42"/>
+      <c r="D7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="87" t="s">
+      <c r="E7" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="88"/>
-    </row>
-    <row r="6" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A6" s="83" t="s">
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="45"/>
+    </row>
+    <row r="8" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A8" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="28"/>
-      <c r="E6" s="79"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="81"/>
-    </row>
-    <row r="7" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A7" s="84"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="28"/>
-      <c r="E7" s="79"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="80"/>
-      <c r="H7" s="81"/>
-    </row>
-    <row r="8" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A8" s="84"/>
       <c r="B8" s="6"/>
       <c r="C8" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D8" s="28"/>
-      <c r="E8" s="79"/>
-      <c r="F8" s="80"/>
-      <c r="G8" s="80"/>
-      <c r="H8" s="81"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="51"/>
     </row>
     <row r="9" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A9" s="84"/>
+      <c r="A9" s="47"/>
       <c r="B9" s="6"/>
-      <c r="C9" s="7" t="s">
-        <v>15</v>
+      <c r="C9" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="D9" s="28"/>
-      <c r="E9" s="79"/>
-      <c r="F9" s="80"/>
-      <c r="G9" s="80"/>
-      <c r="H9" s="81"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="50"/>
+      <c r="H9" s="51"/>
     </row>
     <row r="10" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A10" s="84"/>
+      <c r="A10" s="47"/>
       <c r="B10" s="6"/>
       <c r="C10" s="7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D10" s="28"/>
-      <c r="E10" s="79"/>
-      <c r="F10" s="80"/>
-      <c r="G10" s="80"/>
-      <c r="H10" s="81"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="50"/>
+      <c r="H10" s="51"/>
     </row>
     <row r="11" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A11" s="84"/>
+      <c r="A11" s="47"/>
       <c r="B11" s="6"/>
       <c r="C11" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D11" s="28"/>
-      <c r="E11" s="79"/>
-      <c r="F11" s="80"/>
-      <c r="G11" s="80"/>
-      <c r="H11" s="81"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="51"/>
     </row>
     <row r="12" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A12" s="84"/>
+      <c r="A12" s="47"/>
       <c r="B12" s="6"/>
       <c r="C12" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D12" s="28"/>
-      <c r="E12" s="79"/>
-      <c r="F12" s="80"/>
-      <c r="G12" s="80"/>
-      <c r="H12" s="81"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="51"/>
     </row>
     <row r="13" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A13" s="84"/>
+      <c r="A13" s="47"/>
       <c r="B13" s="6"/>
       <c r="C13" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D13" s="28"/>
-      <c r="E13" s="79"/>
-      <c r="F13" s="80"/>
-      <c r="G13" s="80"/>
-      <c r="H13" s="81"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="51"/>
     </row>
     <row r="14" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A14" s="84"/>
+      <c r="A14" s="47"/>
       <c r="B14" s="6"/>
-      <c r="C14" s="10" t="s">
-        <v>20</v>
+      <c r="C14" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="D14" s="28"/>
-      <c r="E14" s="79"/>
-      <c r="F14" s="80"/>
-      <c r="G14" s="80"/>
-      <c r="H14" s="81"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="51"/>
     </row>
     <row r="15" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A15" s="84"/>
+      <c r="A15" s="47"/>
       <c r="B15" s="6"/>
       <c r="C15" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D15" s="28"/>
-      <c r="E15" s="79"/>
-      <c r="F15" s="80"/>
-      <c r="G15" s="80"/>
-      <c r="H15" s="81"/>
-    </row>
-    <row r="16" spans="1:8" s="10" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A16" s="85"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="50"/>
+      <c r="G15" s="50"/>
+      <c r="H15" s="51"/>
+    </row>
+    <row r="16" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A16" s="47"/>
       <c r="B16" s="6"/>
+      <c r="C16" s="10" t="s">
+        <v>20</v>
+      </c>
       <c r="D16" s="28"/>
-      <c r="E16" s="79"/>
-      <c r="F16" s="80"/>
-      <c r="G16" s="80"/>
-      <c r="H16" s="81"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="50"/>
+      <c r="H16" s="51"/>
     </row>
     <row r="17" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A17" s="83" t="s">
-        <v>22</v>
-      </c>
+      <c r="A17" s="47"/>
       <c r="B17" s="6"/>
       <c r="C17" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D17" s="28"/>
-      <c r="E17" s="79"/>
-      <c r="F17" s="80"/>
-      <c r="G17" s="80"/>
-      <c r="H17" s="81"/>
-    </row>
-    <row r="18" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A18" s="84"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="50"/>
+      <c r="G17" s="50"/>
+      <c r="H17" s="51"/>
+    </row>
+    <row r="18" spans="1:10" s="10" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A18" s="48"/>
       <c r="B18" s="6"/>
-      <c r="C18" s="7" t="s">
-        <v>24</v>
-      </c>
       <c r="D18" s="28"/>
-      <c r="E18" s="79"/>
-      <c r="F18" s="80"/>
-      <c r="G18" s="80"/>
-      <c r="H18" s="81"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="51"/>
     </row>
     <row r="19" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A19" s="84"/>
+      <c r="A19" s="46" t="s">
+        <v>22</v>
+      </c>
       <c r="B19" s="6"/>
       <c r="C19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="28"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="51"/>
+    </row>
+    <row r="20" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A20" s="47"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="28"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="50"/>
+      <c r="H20" s="51"/>
+    </row>
+    <row r="21" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A21" s="47"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="28"/>
-      <c r="E19" s="79"/>
-      <c r="F19" s="80"/>
-      <c r="G19" s="80"/>
-      <c r="H19" s="81"/>
-    </row>
-    <row r="20" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A20" s="84"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="11" t="s">
+      <c r="D21" s="28"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="50"/>
+      <c r="H21" s="51"/>
+    </row>
+    <row r="22" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A22" s="47"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="28"/>
-      <c r="E20" s="79"/>
-      <c r="F20" s="80"/>
-      <c r="G20" s="80"/>
-      <c r="H20" s="81"/>
-    </row>
-    <row r="21" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A21" s="84"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="12" t="s">
+      <c r="D22" s="28"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="51"/>
+    </row>
+    <row r="23" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A23" s="47"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D21" s="28"/>
-      <c r="E21" s="79"/>
-      <c r="F21" s="80"/>
-      <c r="G21" s="80"/>
-      <c r="H21" s="81"/>
-    </row>
-    <row r="22" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A22" s="84"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="79"/>
-      <c r="F22" s="80"/>
-      <c r="G22" s="80"/>
-      <c r="H22" s="81"/>
-    </row>
-    <row r="23" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A23" s="85"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="13"/>
       <c r="D23" s="28"/>
-      <c r="E23" s="79"/>
-      <c r="F23" s="80"/>
-      <c r="G23" s="80"/>
-      <c r="H23" s="81"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="50"/>
+      <c r="H23" s="51"/>
     </row>
     <row r="24" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A24" s="82" t="s">
+      <c r="A24" s="47"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="51"/>
+    </row>
+    <row r="25" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A25" s="48"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="50"/>
+      <c r="H25" s="51"/>
+    </row>
+    <row r="26" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A26" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="7" t="s">
+      <c r="B26" s="6"/>
+      <c r="C26" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="28"/>
-      <c r="E24" s="79"/>
-      <c r="F24" s="80"/>
-      <c r="G24" s="80"/>
-      <c r="H24" s="81"/>
-    </row>
-    <row r="25" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A25" s="82"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" s="28"/>
-      <c r="E25" s="79"/>
-      <c r="F25" s="80"/>
-      <c r="G25" s="80"/>
-      <c r="H25" s="81"/>
-      <c r="J25" s="15"/>
-    </row>
-    <row r="26" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A26" s="82"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="14" t="s">
-        <v>31</v>
-      </c>
       <c r="D26" s="28"/>
-      <c r="E26" s="79"/>
-      <c r="F26" s="80"/>
-      <c r="G26" s="80"/>
-      <c r="H26" s="81"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="50"/>
+      <c r="H26" s="51"/>
     </row>
     <row r="27" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A27" s="82"/>
+      <c r="A27" s="52"/>
       <c r="B27" s="6"/>
       <c r="C27" s="14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D27" s="28"/>
-      <c r="E27" s="79"/>
-      <c r="F27" s="80"/>
-      <c r="G27" s="80"/>
-      <c r="H27" s="81"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="51"/>
+      <c r="J27" s="15"/>
     </row>
     <row r="28" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A28" s="82"/>
+      <c r="A28" s="52"/>
       <c r="B28" s="6"/>
       <c r="C28" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="28"/>
+      <c r="E28" s="49"/>
+      <c r="F28" s="50"/>
+      <c r="G28" s="50"/>
+      <c r="H28" s="51"/>
+    </row>
+    <row r="29" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A29" s="52"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="28"/>
+      <c r="E29" s="49"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="50"/>
+      <c r="H29" s="51"/>
+    </row>
+    <row r="30" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A30" s="52"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="28"/>
-      <c r="E28" s="79"/>
-      <c r="F28" s="80"/>
-      <c r="G28" s="80"/>
-      <c r="H28" s="81"/>
-    </row>
-    <row r="29" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A29" s="82"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="79"/>
-      <c r="F29" s="80"/>
-      <c r="G29" s="80"/>
-      <c r="H29" s="81"/>
-    </row>
-    <row r="30" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A30" s="82"/>
-      <c r="B30" s="6"/>
       <c r="D30" s="28"/>
-      <c r="E30" s="79"/>
-      <c r="F30" s="80"/>
-      <c r="G30" s="80"/>
-      <c r="H30" s="81"/>
+      <c r="E30" s="49"/>
+      <c r="F30" s="50"/>
+      <c r="G30" s="50"/>
+      <c r="H30" s="51"/>
     </row>
     <row r="31" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A31" s="76" t="s">
+      <c r="A31" s="52"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="49"/>
+      <c r="F31" s="50"/>
+      <c r="G31" s="50"/>
+      <c r="H31" s="51"/>
+    </row>
+    <row r="32" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A32" s="52"/>
+      <c r="B32" s="6"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="49"/>
+      <c r="F32" s="50"/>
+      <c r="G32" s="50"/>
+      <c r="H32" s="51"/>
+    </row>
+    <row r="33" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A33" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="16" t="s">
+      <c r="B33" s="6"/>
+      <c r="C33" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D31" s="28"/>
-      <c r="E31" s="79"/>
-      <c r="F31" s="80"/>
-      <c r="G31" s="80"/>
-      <c r="H31" s="81"/>
-    </row>
-    <row r="32" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A32" s="77"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="16" t="s">
+      <c r="D33" s="28"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="50"/>
+      <c r="G33" s="50"/>
+      <c r="H33" s="51"/>
+    </row>
+    <row r="34" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A34" s="54"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D32" s="28"/>
-      <c r="E32" s="79"/>
-      <c r="F32" s="80"/>
-      <c r="G32" s="80"/>
-      <c r="H32" s="81"/>
-    </row>
-    <row r="33" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A33" s="77"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="7" t="s">
+      <c r="D34" s="28"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="50"/>
+      <c r="G34" s="50"/>
+      <c r="H34" s="51"/>
+    </row>
+    <row r="35" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A35" s="54"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D33" s="28"/>
-      <c r="E33" s="79"/>
-      <c r="F33" s="80"/>
-      <c r="G33" s="80"/>
-      <c r="H33" s="81"/>
-    </row>
-    <row r="34" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A34" s="77"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="7" t="s">
+      <c r="D35" s="28"/>
+      <c r="E35" s="49"/>
+      <c r="F35" s="50"/>
+      <c r="G35" s="50"/>
+      <c r="H35" s="51"/>
+    </row>
+    <row r="36" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A36" s="54"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D34" s="28"/>
-      <c r="E34" s="79"/>
-      <c r="F34" s="80"/>
-      <c r="G34" s="80"/>
-      <c r="H34" s="81"/>
-    </row>
-    <row r="35" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A35" s="77"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="79"/>
-      <c r="F35" s="80"/>
-      <c r="G35" s="80"/>
-      <c r="H35" s="81"/>
-    </row>
-    <row r="36" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A36" s="78"/>
-      <c r="B36" s="6"/>
       <c r="D36" s="28"/>
-      <c r="E36" s="79"/>
-      <c r="F36" s="80"/>
-      <c r="G36" s="80"/>
-      <c r="H36" s="81"/>
+      <c r="E36" s="49"/>
+      <c r="F36" s="50"/>
+      <c r="G36" s="50"/>
+      <c r="H36" s="51"/>
     </row>
     <row r="37" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A37" s="76" t="s">
+      <c r="A37" s="54"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="49"/>
+      <c r="F37" s="50"/>
+      <c r="G37" s="50"/>
+      <c r="H37" s="51"/>
+    </row>
+    <row r="38" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A38" s="55"/>
+      <c r="B38" s="6"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="49"/>
+      <c r="F38" s="50"/>
+      <c r="G38" s="50"/>
+      <c r="H38" s="51"/>
+    </row>
+    <row r="39" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A39" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="6"/>
-      <c r="C37" s="7" t="s">
+      <c r="B39" s="6"/>
+      <c r="C39" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D37" s="28"/>
-      <c r="E37" s="79"/>
-      <c r="F37" s="80"/>
-      <c r="G37" s="80"/>
-      <c r="H37" s="81"/>
-    </row>
-    <row r="38" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A38" s="77"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="7" t="s">
+      <c r="D39" s="28"/>
+      <c r="E39" s="49"/>
+      <c r="F39" s="50"/>
+      <c r="G39" s="50"/>
+      <c r="H39" s="51"/>
+    </row>
+    <row r="40" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A40" s="54"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D38" s="28"/>
-      <c r="E38" s="79"/>
-      <c r="F38" s="80"/>
-      <c r="G38" s="80"/>
-      <c r="H38" s="81"/>
-    </row>
-    <row r="39" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A39" s="77"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="17" t="s">
+      <c r="D40" s="28"/>
+      <c r="E40" s="49"/>
+      <c r="F40" s="50"/>
+      <c r="G40" s="50"/>
+      <c r="H40" s="51"/>
+    </row>
+    <row r="41" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A41" s="54"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D39" s="28"/>
-      <c r="E39" s="79"/>
-      <c r="F39" s="80"/>
-      <c r="G39" s="80"/>
-      <c r="H39" s="81"/>
-    </row>
-    <row r="40" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A40" s="77"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="79"/>
-      <c r="F40" s="80"/>
-      <c r="G40" s="80"/>
-      <c r="H40" s="81"/>
-    </row>
-    <row r="41" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A41" s="78"/>
-      <c r="B41" s="18"/>
-      <c r="D41" s="29"/>
-      <c r="E41" s="79"/>
-      <c r="F41" s="80"/>
-      <c r="G41" s="80"/>
-      <c r="H41" s="81"/>
+      <c r="D41" s="28"/>
+      <c r="E41" s="49"/>
+      <c r="F41" s="50"/>
+      <c r="G41" s="50"/>
+      <c r="H41" s="51"/>
     </row>
     <row r="42" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A42" s="68"/>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="70"/>
-      <c r="F42" s="70"/>
-      <c r="G42" s="70"/>
-      <c r="H42" s="71"/>
-    </row>
-    <row r="43" spans="1:8" ht="9" customHeight="1">
-      <c r="A43" s="69"/>
-      <c r="B43" s="20"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="72"/>
-      <c r="F43" s="72"/>
-      <c r="G43" s="72"/>
-      <c r="H43" s="73"/>
-    </row>
-    <row r="44" spans="1:8" ht="9" customHeight="1">
-      <c r="A44" s="69"/>
-      <c r="B44" s="20"/>
-      <c r="C44" s="20"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="72"/>
-      <c r="F44" s="72"/>
-      <c r="G44" s="72"/>
-      <c r="H44" s="73"/>
+      <c r="A42" s="54"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="28"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="50"/>
+      <c r="G42" s="50"/>
+      <c r="H42" s="51"/>
+    </row>
+    <row r="43" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A43" s="55"/>
+      <c r="B43" s="18"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="50"/>
+      <c r="G43" s="50"/>
+      <c r="H43" s="51"/>
+    </row>
+    <row r="44" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
+      <c r="A44" s="56"/>
+      <c r="B44" s="19"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="58"/>
+      <c r="F44" s="58"/>
+      <c r="G44" s="58"/>
+      <c r="H44" s="59"/>
     </row>
     <row r="45" spans="1:8" ht="9" customHeight="1">
-      <c r="A45" s="69"/>
+      <c r="A45" s="57"/>
       <c r="B45" s="20"/>
       <c r="C45" s="20"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="74"/>
-      <c r="F45" s="74"/>
-      <c r="G45" s="74"/>
-      <c r="H45" s="75"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="60"/>
+      <c r="F45" s="60"/>
+      <c r="G45" s="60"/>
+      <c r="H45" s="61"/>
     </row>
     <row r="46" spans="1:8" ht="9" customHeight="1">
-      <c r="A46" s="69"/>
-      <c r="B46" s="23"/>
-      <c r="C46" s="23"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="74"/>
-      <c r="F46" s="74"/>
-      <c r="G46" s="74"/>
-      <c r="H46" s="75"/>
+      <c r="A46" s="57"/>
+      <c r="B46" s="20"/>
+      <c r="C46" s="20"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="60"/>
+      <c r="F46" s="60"/>
+      <c r="G46" s="60"/>
+      <c r="H46" s="61"/>
     </row>
     <row r="47" spans="1:8" ht="9" customHeight="1">
-      <c r="A47" s="47" t="s">
+      <c r="A47" s="57"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="62"/>
+      <c r="F47" s="62"/>
+      <c r="G47" s="62"/>
+      <c r="H47" s="63"/>
+    </row>
+    <row r="48" spans="1:8" ht="9" customHeight="1">
+      <c r="A48" s="57"/>
+      <c r="B48" s="23"/>
+      <c r="C48" s="23"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="62"/>
+      <c r="F48" s="62"/>
+      <c r="G48" s="62"/>
+      <c r="H48" s="63"/>
+    </row>
+    <row r="49" spans="1:8" ht="9" customHeight="1">
+      <c r="A49" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="48"/>
-      <c r="C47" s="49"/>
-      <c r="D47" s="56" t="s">
+      <c r="B49" s="65"/>
+      <c r="C49" s="66"/>
+      <c r="D49" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="E47" s="56"/>
-      <c r="F47" s="56"/>
-      <c r="G47" s="56"/>
-      <c r="H47" s="57"/>
-    </row>
-    <row r="48" spans="1:8" ht="9" customHeight="1">
-      <c r="A48" s="50"/>
-      <c r="B48" s="51"/>
-      <c r="C48" s="52"/>
-      <c r="D48" s="24" t="s">
+      <c r="E49" s="73"/>
+      <c r="F49" s="73"/>
+      <c r="G49" s="73"/>
+      <c r="H49" s="74"/>
+    </row>
+    <row r="50" spans="1:8" ht="9" customHeight="1">
+      <c r="A50" s="67"/>
+      <c r="B50" s="68"/>
+      <c r="C50" s="69"/>
+      <c r="D50" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E48" s="58"/>
-      <c r="F48" s="58"/>
-      <c r="G48" s="59"/>
-      <c r="H48" s="25" t="s">
+      <c r="E50" s="44"/>
+      <c r="F50" s="44"/>
+      <c r="G50" s="75"/>
+      <c r="H50" s="25" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="9" customHeight="1">
-      <c r="A49" s="50"/>
-      <c r="B49" s="51"/>
-      <c r="C49" s="52"/>
-      <c r="D49" s="60"/>
-      <c r="E49" s="61"/>
-      <c r="F49" s="61"/>
-      <c r="G49" s="62"/>
-      <c r="H49" s="26"/>
-    </row>
-    <row r="50" spans="1:8" ht="9" customHeight="1">
-      <c r="A50" s="50"/>
-      <c r="B50" s="51"/>
-      <c r="C50" s="52"/>
-      <c r="D50" s="60"/>
-      <c r="E50" s="61"/>
-      <c r="F50" s="61"/>
-      <c r="G50" s="62"/>
-      <c r="H50" s="26"/>
-    </row>
     <row r="51" spans="1:8" ht="9" customHeight="1">
-      <c r="A51" s="50"/>
-      <c r="B51" s="51"/>
-      <c r="C51" s="52"/>
-      <c r="D51" s="60"/>
-      <c r="E51" s="61"/>
-      <c r="F51" s="61"/>
-      <c r="G51" s="62"/>
+      <c r="A51" s="67"/>
+      <c r="B51" s="68"/>
+      <c r="C51" s="69"/>
+      <c r="D51" s="76"/>
+      <c r="E51" s="77"/>
+      <c r="F51" s="77"/>
+      <c r="G51" s="78"/>
       <c r="H51" s="26"/>
     </row>
     <row r="52" spans="1:8" ht="9" customHeight="1">
-      <c r="A52" s="50"/>
-      <c r="B52" s="51"/>
-      <c r="C52" s="52"/>
-      <c r="D52" s="60"/>
-      <c r="E52" s="61"/>
-      <c r="F52" s="61"/>
-      <c r="G52" s="62"/>
+      <c r="A52" s="67"/>
+      <c r="B52" s="68"/>
+      <c r="C52" s="69"/>
+      <c r="D52" s="76"/>
+      <c r="E52" s="77"/>
+      <c r="F52" s="77"/>
+      <c r="G52" s="78"/>
       <c r="H52" s="26"/>
     </row>
     <row r="53" spans="1:8" ht="9" customHeight="1">
-      <c r="A53" s="50"/>
-      <c r="B53" s="51"/>
-      <c r="C53" s="52"/>
-      <c r="D53" s="60"/>
-      <c r="E53" s="61"/>
-      <c r="F53" s="61"/>
-      <c r="G53" s="62"/>
+      <c r="A53" s="67"/>
+      <c r="B53" s="68"/>
+      <c r="C53" s="69"/>
+      <c r="D53" s="76"/>
+      <c r="E53" s="77"/>
+      <c r="F53" s="77"/>
+      <c r="G53" s="78"/>
       <c r="H53" s="26"/>
     </row>
     <row r="54" spans="1:8" ht="9" customHeight="1">
-      <c r="A54" s="50"/>
-      <c r="B54" s="51"/>
-      <c r="C54" s="52"/>
-      <c r="D54" s="63"/>
-      <c r="E54" s="64"/>
-      <c r="F54" s="64"/>
-      <c r="G54" s="62"/>
+      <c r="A54" s="67"/>
+      <c r="B54" s="68"/>
+      <c r="C54" s="69"/>
+      <c r="D54" s="76"/>
+      <c r="E54" s="77"/>
+      <c r="F54" s="77"/>
+      <c r="G54" s="78"/>
       <c r="H54" s="26"/>
     </row>
     <row r="55" spans="1:8" ht="9" customHeight="1">
-      <c r="A55" s="50"/>
-      <c r="B55" s="51"/>
-      <c r="C55" s="52"/>
-      <c r="D55" s="65" t="s">
+      <c r="A55" s="67"/>
+      <c r="B55" s="68"/>
+      <c r="C55" s="69"/>
+      <c r="D55" s="76"/>
+      <c r="E55" s="77"/>
+      <c r="F55" s="77"/>
+      <c r="G55" s="78"/>
+      <c r="H55" s="26"/>
+    </row>
+    <row r="56" spans="1:8" ht="9" customHeight="1">
+      <c r="A56" s="67"/>
+      <c r="B56" s="68"/>
+      <c r="C56" s="69"/>
+      <c r="D56" s="79"/>
+      <c r="E56" s="80"/>
+      <c r="F56" s="80"/>
+      <c r="G56" s="78"/>
+      <c r="H56" s="26"/>
+    </row>
+    <row r="57" spans="1:8" ht="9" customHeight="1">
+      <c r="A57" s="67"/>
+      <c r="B57" s="68"/>
+      <c r="C57" s="69"/>
+      <c r="D57" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="E55" s="66"/>
-      <c r="F55" s="67"/>
-      <c r="G55" s="32"/>
-      <c r="H55" s="33"/>
-    </row>
-    <row r="56" spans="1:8" ht="9" customHeight="1">
-      <c r="A56" s="50"/>
-      <c r="B56" s="51"/>
-      <c r="C56" s="52"/>
-      <c r="D56" s="36" t="s">
+      <c r="E57" s="82"/>
+      <c r="F57" s="83"/>
+      <c r="G57" s="85"/>
+      <c r="H57" s="86"/>
+    </row>
+    <row r="58" spans="1:8" ht="9" customHeight="1">
+      <c r="A58" s="67"/>
+      <c r="B58" s="68"/>
+      <c r="C58" s="69"/>
+      <c r="D58" s="89" t="s">
         <v>48</v>
       </c>
-      <c r="E56" s="37"/>
-      <c r="F56" s="38"/>
-      <c r="G56" s="34"/>
-      <c r="H56" s="35"/>
-    </row>
-    <row r="57" spans="1:8" ht="9" customHeight="1">
-      <c r="A57" s="50"/>
-      <c r="B57" s="51"/>
-      <c r="C57" s="52"/>
-      <c r="D57" s="39" t="s">
+      <c r="E58" s="90"/>
+      <c r="F58" s="91"/>
+      <c r="G58" s="87"/>
+      <c r="H58" s="88"/>
+    </row>
+    <row r="59" spans="1:8" ht="9" customHeight="1">
+      <c r="A59" s="67"/>
+      <c r="B59" s="68"/>
+      <c r="C59" s="69"/>
+      <c r="D59" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="E57" s="40"/>
-      <c r="F57" s="41"/>
-      <c r="G57" s="32"/>
-      <c r="H57" s="33"/>
-    </row>
-    <row r="58" spans="1:8" ht="9" customHeight="1">
-      <c r="A58" s="50"/>
-      <c r="B58" s="51"/>
-      <c r="C58" s="52"/>
-      <c r="D58" s="36" t="s">
+      <c r="E59" s="93"/>
+      <c r="F59" s="94"/>
+      <c r="G59" s="85"/>
+      <c r="H59" s="86"/>
+    </row>
+    <row r="60" spans="1:8" ht="9" customHeight="1">
+      <c r="A60" s="67"/>
+      <c r="B60" s="68"/>
+      <c r="C60" s="69"/>
+      <c r="D60" s="89" t="s">
         <v>50</v>
       </c>
-      <c r="E58" s="37"/>
-      <c r="F58" s="38"/>
-      <c r="G58" s="34"/>
-      <c r="H58" s="35"/>
-    </row>
-    <row r="59" spans="1:8" ht="9" customHeight="1">
-      <c r="A59" s="50"/>
-      <c r="B59" s="51"/>
-      <c r="C59" s="52"/>
-      <c r="D59" s="40" t="s">
+      <c r="E60" s="90"/>
+      <c r="F60" s="91"/>
+      <c r="G60" s="87"/>
+      <c r="H60" s="88"/>
+    </row>
+    <row r="61" spans="1:8" ht="9" customHeight="1">
+      <c r="A61" s="67"/>
+      <c r="B61" s="68"/>
+      <c r="C61" s="69"/>
+      <c r="D61" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="E59" s="40"/>
-      <c r="F59" s="41"/>
-      <c r="G59" s="32"/>
-      <c r="H59" s="33"/>
-    </row>
-    <row r="60" spans="1:8" ht="9" customHeight="1" thickBot="1">
-      <c r="A60" s="53"/>
-      <c r="B60" s="54"/>
-      <c r="C60" s="55"/>
-      <c r="D60" s="44" t="s">
+      <c r="E61" s="93"/>
+      <c r="F61" s="94"/>
+      <c r="G61" s="85"/>
+      <c r="H61" s="86"/>
+    </row>
+    <row r="62" spans="1:8" ht="9" customHeight="1" thickBot="1">
+      <c r="A62" s="70"/>
+      <c r="B62" s="71"/>
+      <c r="C62" s="72"/>
+      <c r="D62" s="97" t="s">
         <v>52</v>
       </c>
-      <c r="E60" s="45"/>
-      <c r="F60" s="46"/>
-      <c r="G60" s="42"/>
-      <c r="H60" s="43"/>
-    </row>
-    <row r="61" spans="1:8" ht="9" customHeight="1" thickTop="1">
-      <c r="F61" s="31" t="s">
+      <c r="E62" s="98"/>
+      <c r="F62" s="99"/>
+      <c r="G62" s="95"/>
+      <c r="H62" s="96"/>
+    </row>
+    <row r="63" spans="1:8" ht="9" customHeight="1" thickTop="1">
+      <c r="F63" s="84" t="s">
         <v>53</v>
       </c>
-      <c r="G61" s="31"/>
-      <c r="H61" s="31"/>
-    </row>
-    <row r="62" spans="1:8" ht="9" customHeight="1">
-      <c r="A62"/>
-      <c r="B62"/>
-      <c r="C62"/>
-      <c r="D62"/>
-      <c r="E62"/>
-      <c r="F62"/>
-      <c r="G62"/>
-      <c r="H62"/>
-    </row>
-    <row r="63" spans="1:8">
-      <c r="A63"/>
-      <c r="B63"/>
-      <c r="C63"/>
-      <c r="D63"/>
-      <c r="E63"/>
-      <c r="F63"/>
-      <c r="G63"/>
-      <c r="H63"/>
-    </row>
-    <row r="64" spans="1:8">
+      <c r="G63" s="84"/>
+      <c r="H63" s="84"/>
+    </row>
+    <row r="64" spans="1:8" ht="9" customHeight="1">
       <c r="A64"/>
       <c r="B64"/>
       <c r="C64"/>
@@ -2122,25 +2150,135 @@
       <c r="G64"/>
       <c r="H64"/>
     </row>
-    <row r="65" customFormat="1"/>
-    <row r="66" customFormat="1"/>
-    <row r="67" customFormat="1"/>
-    <row r="68" customFormat="1"/>
-    <row r="69" customFormat="1"/>
+    <row r="65" spans="1:8">
+      <c r="A65"/>
+      <c r="B65"/>
+      <c r="C65"/>
+      <c r="D65"/>
+      <c r="E65"/>
+      <c r="F65"/>
+      <c r="G65"/>
+      <c r="H65"/>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66"/>
+      <c r="B66"/>
+      <c r="C66"/>
+      <c r="D66"/>
+      <c r="E66"/>
+      <c r="F66"/>
+      <c r="G66"/>
+      <c r="H66"/>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67"/>
+      <c r="B67"/>
+      <c r="C67"/>
+      <c r="D67"/>
+      <c r="E67"/>
+      <c r="F67"/>
+      <c r="G67"/>
+      <c r="H67"/>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68"/>
+      <c r="B68"/>
+      <c r="C68"/>
+      <c r="D68"/>
+      <c r="E68"/>
+      <c r="F68"/>
+      <c r="G68"/>
+      <c r="H68"/>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69"/>
+      <c r="B69"/>
+      <c r="C69"/>
+      <c r="D69"/>
+      <c r="E69"/>
+      <c r="F69"/>
+      <c r="G69"/>
+      <c r="H69"/>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70"/>
+      <c r="B70"/>
+      <c r="C70"/>
+      <c r="D70"/>
+      <c r="E70"/>
+      <c r="F70"/>
+      <c r="G70"/>
+      <c r="H70"/>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71"/>
+      <c r="B71"/>
+      <c r="C71"/>
+      <c r="D71"/>
+      <c r="E71"/>
+      <c r="F71"/>
+      <c r="G71"/>
+      <c r="H71"/>
+    </row>
   </sheetData>
-  <mergeCells count="75">
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="A6:A16"/>
-    <mergeCell ref="E6:H6"/>
+  <mergeCells count="79">
+    <mergeCell ref="F63:H63"/>
+    <mergeCell ref="G57:H58"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="G59:H60"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="G61:H62"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="A49:C62"/>
+    <mergeCell ref="D49:H49"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="D51:G51"/>
+    <mergeCell ref="D52:G52"/>
+    <mergeCell ref="D53:G53"/>
+    <mergeCell ref="D54:G54"/>
+    <mergeCell ref="D55:G55"/>
+    <mergeCell ref="D56:G56"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="A44:A48"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="A39:A43"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="A33:A38"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="A26:A32"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="A19:A25"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="B7:C7"/>
     <mergeCell ref="E7:H7"/>
+    <mergeCell ref="A8:A18"/>
     <mergeCell ref="E8:H8"/>
     <mergeCell ref="E9:H9"/>
     <mergeCell ref="E10:H10"/>
@@ -2150,60 +2288,19 @@
     <mergeCell ref="E14:H14"/>
     <mergeCell ref="E15:H15"/>
     <mergeCell ref="E16:H16"/>
-    <mergeCell ref="A17:A23"/>
     <mergeCell ref="E17:H17"/>
     <mergeCell ref="E18:H18"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="A24:A30"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="A31:A36"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="A37:A41"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="A42:A46"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="A47:C60"/>
-    <mergeCell ref="D47:H47"/>
-    <mergeCell ref="E48:G48"/>
-    <mergeCell ref="D49:G49"/>
-    <mergeCell ref="D50:G50"/>
-    <mergeCell ref="D51:G51"/>
-    <mergeCell ref="D52:G52"/>
-    <mergeCell ref="D53:G53"/>
-    <mergeCell ref="D54:G54"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="F61:H61"/>
-    <mergeCell ref="G55:H56"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="G57:H58"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="G59:H60"/>
-    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F5:H5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.195138888888889" bottom="0" header="0" footer="0"/>

--- a/public/assets/templates/maintenance/electrical.xlsx
+++ b/public/assets/templates/maintenance/electrical.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2D4D562-585D-497D-A19C-6947134E6EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D425089-7679-486B-9C6F-93017B77A7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{1839BE4E-8ABA-4E0E-BDE7-D891D69ECECB}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="60">
   <si>
     <t>LAPORAN MAINTENANCE ELECTRICAL</t>
   </si>
@@ -202,6 +202,9 @@
   </si>
   <si>
     <t>Lokasi</t>
+  </si>
+  <si>
+    <t>MID</t>
   </si>
 </sst>
 </file>
@@ -304,7 +307,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -561,19 +564,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -706,7 +696,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -779,9 +769,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -800,6 +787,162 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -833,179 +976,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1377,40 +1349,40 @@
   <dimension ref="A1:J71"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" style="27" customWidth="1"/>
-    <col min="2" max="2" width="3" style="27" customWidth="1"/>
-    <col min="3" max="3" width="23" style="27" customWidth="1"/>
-    <col min="4" max="4" width="6.26953125" style="27" customWidth="1"/>
-    <col min="5" max="5" width="2.26953125" style="27" customWidth="1"/>
-    <col min="6" max="6" width="15.26953125" style="27" customWidth="1"/>
-    <col min="7" max="7" width="4.7265625" style="27" customWidth="1"/>
-    <col min="8" max="8" width="6" style="27" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="3" style="26" customWidth="1"/>
+    <col min="3" max="3" width="23" style="26" customWidth="1"/>
+    <col min="4" max="4" width="6.26953125" style="26" customWidth="1"/>
+    <col min="5" max="5" width="2.26953125" style="26" customWidth="1"/>
+    <col min="6" max="6" width="15.26953125" style="26" customWidth="1"/>
+    <col min="7" max="7" width="4.7265625" style="26" customWidth="1"/>
+    <col min="8" max="8" width="6" style="26" customWidth="1"/>
     <col min="12" max="12" width="10.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" thickTop="1">
-      <c r="A1" s="34"/>
-      <c r="B1" s="35"/>
-      <c r="C1" s="38" t="s">
+      <c r="A1" s="85"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="89" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="39"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="90"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="36"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="40" t="s">
+      <c r="A2" s="87"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="91" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="41"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="92"/>
     </row>
     <row r="3" spans="1:8" ht="10.25" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -1420,15 +1392,15 @@
         <v>2</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="31"/>
-      <c r="F3" s="32" t="s">
+      <c r="E3" s="82"/>
+      <c r="F3" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="32"/>
-      <c r="H3" s="33"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="84"/>
     </row>
     <row r="4" spans="1:8" ht="10.25" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -1438,15 +1410,15 @@
         <v>2</v>
       </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="82" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="31"/>
-      <c r="F4" s="32" t="s">
+      <c r="E4" s="82"/>
+      <c r="F4" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="32"/>
-      <c r="H4" s="33"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="84"/>
     </row>
     <row r="5" spans="1:8" ht="10.25" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -1456,15 +1428,15 @@
         <v>2</v>
       </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="32" t="s">
+      <c r="E5" s="82"/>
+      <c r="F5" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="G5" s="32"/>
-      <c r="H5" s="33"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="84"/>
     </row>
     <row r="6" spans="1:8" ht="10.25" customHeight="1">
       <c r="A6" s="1" t="s">
@@ -1474,671 +1446,673 @@
         <v>2</v>
       </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="31"/>
-      <c r="F6" s="32" t="s">
+      <c r="E6" s="82"/>
+      <c r="F6" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="32"/>
-      <c r="H6" s="33"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="84"/>
     </row>
     <row r="7" spans="1:8" s="5" customFormat="1" ht="10.25" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="42"/>
+      <c r="C7" s="79"/>
       <c r="D7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="80" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="45"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="81"/>
     </row>
     <row r="8" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A8" s="46" t="s">
+      <c r="A8" s="76" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="28"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="51"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="73"/>
+      <c r="G8" s="73"/>
+      <c r="H8" s="74"/>
     </row>
     <row r="9" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A9" s="47"/>
+      <c r="A9" s="77"/>
       <c r="B9" s="6"/>
       <c r="C9" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="28"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="51"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="73"/>
+      <c r="G9" s="73"/>
+      <c r="H9" s="74"/>
     </row>
     <row r="10" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A10" s="47"/>
+      <c r="A10" s="77"/>
       <c r="B10" s="6"/>
       <c r="C10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="28"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="51"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="73"/>
+      <c r="H10" s="74"/>
     </row>
     <row r="11" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A11" s="47"/>
+      <c r="A11" s="77"/>
       <c r="B11" s="6"/>
       <c r="C11" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="28"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="51"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="73"/>
+      <c r="H11" s="74"/>
     </row>
     <row r="12" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A12" s="47"/>
+      <c r="A12" s="77"/>
       <c r="B12" s="6"/>
       <c r="C12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="28"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="51"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="74"/>
     </row>
     <row r="13" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A13" s="47"/>
+      <c r="A13" s="77"/>
       <c r="B13" s="6"/>
       <c r="C13" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="28"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="51"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="74"/>
     </row>
     <row r="14" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A14" s="47"/>
+      <c r="A14" s="77"/>
       <c r="B14" s="6"/>
       <c r="C14" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="28"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="51"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="73"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="74"/>
     </row>
     <row r="15" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A15" s="47"/>
+      <c r="A15" s="77"/>
       <c r="B15" s="6"/>
       <c r="C15" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="28"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="51"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="72"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
+      <c r="H15" s="74"/>
     </row>
     <row r="16" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A16" s="47"/>
+      <c r="A16" s="77"/>
       <c r="B16" s="6"/>
       <c r="C16" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="28"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="51"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="72"/>
+      <c r="F16" s="73"/>
+      <c r="G16" s="73"/>
+      <c r="H16" s="74"/>
     </row>
     <row r="17" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A17" s="47"/>
+      <c r="A17" s="77"/>
       <c r="B17" s="6"/>
       <c r="C17" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="28"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="50"/>
-      <c r="H17" s="51"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="72"/>
+      <c r="F17" s="73"/>
+      <c r="G17" s="73"/>
+      <c r="H17" s="74"/>
     </row>
     <row r="18" spans="1:10" s="10" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A18" s="48"/>
+      <c r="A18" s="78"/>
       <c r="B18" s="6"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="51"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="72"/>
+      <c r="F18" s="73"/>
+      <c r="G18" s="73"/>
+      <c r="H18" s="74"/>
     </row>
     <row r="19" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A19" s="46" t="s">
+      <c r="A19" s="76" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="28"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="51"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="72"/>
+      <c r="F19" s="73"/>
+      <c r="G19" s="73"/>
+      <c r="H19" s="74"/>
     </row>
     <row r="20" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A20" s="47"/>
+      <c r="A20" s="77"/>
       <c r="B20" s="6"/>
       <c r="C20" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="28"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="51"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="72"/>
+      <c r="F20" s="73"/>
+      <c r="G20" s="73"/>
+      <c r="H20" s="74"/>
     </row>
     <row r="21" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A21" s="47"/>
+      <c r="A21" s="77"/>
       <c r="B21" s="6"/>
       <c r="C21" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="28"/>
-      <c r="E21" s="49"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="50"/>
-      <c r="H21" s="51"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="72"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="73"/>
+      <c r="H21" s="74"/>
     </row>
     <row r="22" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A22" s="47"/>
+      <c r="A22" s="77"/>
       <c r="B22" s="6"/>
       <c r="C22" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="28"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="50"/>
-      <c r="G22" s="50"/>
-      <c r="H22" s="51"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="73"/>
+      <c r="H22" s="74"/>
     </row>
     <row r="23" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A23" s="47"/>
+      <c r="A23" s="77"/>
       <c r="B23" s="6"/>
       <c r="C23" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D23" s="28"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="50"/>
-      <c r="H23" s="51"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="73"/>
+      <c r="H23" s="74"/>
     </row>
     <row r="24" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A24" s="47"/>
+      <c r="A24" s="77"/>
       <c r="B24" s="6"/>
       <c r="C24" s="7"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="49"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="51"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="73"/>
+      <c r="G24" s="73"/>
+      <c r="H24" s="74"/>
     </row>
     <row r="25" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A25" s="48"/>
+      <c r="A25" s="78"/>
       <c r="B25" s="6"/>
       <c r="C25" s="13"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="51"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="72"/>
+      <c r="F25" s="73"/>
+      <c r="G25" s="73"/>
+      <c r="H25" s="74"/>
     </row>
     <row r="26" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A26" s="52" t="s">
+      <c r="A26" s="75" t="s">
         <v>28</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D26" s="28"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="50"/>
-      <c r="G26" s="50"/>
-      <c r="H26" s="51"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="72"/>
+      <c r="F26" s="73"/>
+      <c r="G26" s="73"/>
+      <c r="H26" s="74"/>
     </row>
     <row r="27" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A27" s="52"/>
+      <c r="A27" s="75"/>
       <c r="B27" s="6"/>
       <c r="C27" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="28"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="51"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="72"/>
+      <c r="F27" s="73"/>
+      <c r="G27" s="73"/>
+      <c r="H27" s="74"/>
       <c r="J27" s="15"/>
     </row>
     <row r="28" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A28" s="52"/>
+      <c r="A28" s="75"/>
       <c r="B28" s="6"/>
       <c r="C28" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="28"/>
-      <c r="E28" s="49"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="51"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="72"/>
+      <c r="F28" s="73"/>
+      <c r="G28" s="73"/>
+      <c r="H28" s="74"/>
     </row>
     <row r="29" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A29" s="52"/>
+      <c r="A29" s="75"/>
       <c r="B29" s="6"/>
       <c r="C29" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D29" s="28"/>
-      <c r="E29" s="49"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="50"/>
-      <c r="H29" s="51"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="72"/>
+      <c r="F29" s="73"/>
+      <c r="G29" s="73"/>
+      <c r="H29" s="74"/>
     </row>
     <row r="30" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A30" s="52"/>
+      <c r="A30" s="75"/>
       <c r="B30" s="6"/>
       <c r="C30" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D30" s="28"/>
-      <c r="E30" s="49"/>
-      <c r="F30" s="50"/>
-      <c r="G30" s="50"/>
-      <c r="H30" s="51"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="72"/>
+      <c r="F30" s="73"/>
+      <c r="G30" s="73"/>
+      <c r="H30" s="74"/>
     </row>
     <row r="31" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A31" s="52"/>
+      <c r="A31" s="75"/>
       <c r="B31" s="6"/>
       <c r="C31" s="14"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="49"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="50"/>
-      <c r="H31" s="51"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="72"/>
+      <c r="F31" s="73"/>
+      <c r="G31" s="73"/>
+      <c r="H31" s="74"/>
     </row>
     <row r="32" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A32" s="52"/>
+      <c r="A32" s="75"/>
       <c r="B32" s="6"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="49"/>
-      <c r="F32" s="50"/>
-      <c r="G32" s="50"/>
-      <c r="H32" s="51"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="72"/>
+      <c r="F32" s="73"/>
+      <c r="G32" s="73"/>
+      <c r="H32" s="74"/>
     </row>
     <row r="33" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A33" s="53" t="s">
+      <c r="A33" s="69" t="s">
         <v>34</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D33" s="28"/>
-      <c r="E33" s="49"/>
-      <c r="F33" s="50"/>
-      <c r="G33" s="50"/>
-      <c r="H33" s="51"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="72"/>
+      <c r="F33" s="73"/>
+      <c r="G33" s="73"/>
+      <c r="H33" s="74"/>
     </row>
     <row r="34" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A34" s="54"/>
+      <c r="A34" s="70"/>
       <c r="B34" s="6"/>
       <c r="C34" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D34" s="28"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="50"/>
-      <c r="G34" s="50"/>
-      <c r="H34" s="51"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="72"/>
+      <c r="F34" s="73"/>
+      <c r="G34" s="73"/>
+      <c r="H34" s="74"/>
     </row>
     <row r="35" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A35" s="54"/>
+      <c r="A35" s="70"/>
       <c r="B35" s="6"/>
       <c r="C35" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D35" s="28"/>
-      <c r="E35" s="49"/>
-      <c r="F35" s="50"/>
-      <c r="G35" s="50"/>
-      <c r="H35" s="51"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="72"/>
+      <c r="F35" s="73"/>
+      <c r="G35" s="73"/>
+      <c r="H35" s="74"/>
     </row>
     <row r="36" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A36" s="54"/>
+      <c r="A36" s="70"/>
       <c r="B36" s="6"/>
       <c r="C36" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D36" s="28"/>
-      <c r="E36" s="49"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="51"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="72"/>
+      <c r="F36" s="73"/>
+      <c r="G36" s="73"/>
+      <c r="H36" s="74"/>
     </row>
     <row r="37" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A37" s="54"/>
+      <c r="A37" s="70"/>
       <c r="B37" s="6"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="49"/>
-      <c r="F37" s="50"/>
-      <c r="G37" s="50"/>
-      <c r="H37" s="51"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="72"/>
+      <c r="F37" s="73"/>
+      <c r="G37" s="73"/>
+      <c r="H37" s="74"/>
     </row>
     <row r="38" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A38" s="55"/>
+      <c r="A38" s="71"/>
       <c r="B38" s="6"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="49"/>
-      <c r="F38" s="50"/>
-      <c r="G38" s="50"/>
-      <c r="H38" s="51"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="72"/>
+      <c r="F38" s="73"/>
+      <c r="G38" s="73"/>
+      <c r="H38" s="74"/>
     </row>
     <row r="39" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A39" s="53" t="s">
+      <c r="A39" s="69" t="s">
         <v>39</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D39" s="28"/>
-      <c r="E39" s="49"/>
-      <c r="F39" s="50"/>
-      <c r="G39" s="50"/>
-      <c r="H39" s="51"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="72"/>
+      <c r="F39" s="73"/>
+      <c r="G39" s="73"/>
+      <c r="H39" s="74"/>
     </row>
     <row r="40" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A40" s="54"/>
+      <c r="A40" s="70"/>
       <c r="B40" s="6"/>
       <c r="C40" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D40" s="28"/>
-      <c r="E40" s="49"/>
-      <c r="F40" s="50"/>
-      <c r="G40" s="50"/>
-      <c r="H40" s="51"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="72"/>
+      <c r="F40" s="73"/>
+      <c r="G40" s="73"/>
+      <c r="H40" s="74"/>
     </row>
     <row r="41" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A41" s="54"/>
+      <c r="A41" s="70"/>
       <c r="B41" s="6"/>
       <c r="C41" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D41" s="28"/>
-      <c r="E41" s="49"/>
-      <c r="F41" s="50"/>
-      <c r="G41" s="50"/>
-      <c r="H41" s="51"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="72"/>
+      <c r="F41" s="73"/>
+      <c r="G41" s="73"/>
+      <c r="H41" s="74"/>
     </row>
     <row r="42" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A42" s="54"/>
+      <c r="A42" s="70"/>
       <c r="B42" s="6"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="49"/>
-      <c r="F42" s="50"/>
-      <c r="G42" s="50"/>
-      <c r="H42" s="51"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="72"/>
+      <c r="F42" s="73"/>
+      <c r="G42" s="73"/>
+      <c r="H42" s="74"/>
     </row>
     <row r="43" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A43" s="55"/>
+      <c r="A43" s="71"/>
       <c r="B43" s="18"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="49"/>
-      <c r="F43" s="50"/>
-      <c r="G43" s="50"/>
-      <c r="H43" s="51"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="72"/>
+      <c r="F43" s="73"/>
+      <c r="G43" s="73"/>
+      <c r="H43" s="74"/>
     </row>
     <row r="44" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A44" s="56"/>
+      <c r="A44" s="61"/>
       <c r="B44" s="19"/>
       <c r="C44" s="19"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="58"/>
-      <c r="F44" s="58"/>
-      <c r="G44" s="58"/>
-      <c r="H44" s="59"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="63"/>
+      <c r="F44" s="63"/>
+      <c r="G44" s="63"/>
+      <c r="H44" s="64"/>
     </row>
     <row r="45" spans="1:8" ht="9" customHeight="1">
-      <c r="A45" s="57"/>
+      <c r="A45" s="62"/>
       <c r="B45" s="20"/>
       <c r="C45" s="20"/>
       <c r="D45" s="21"/>
-      <c r="E45" s="60"/>
-      <c r="F45" s="60"/>
-      <c r="G45" s="60"/>
-      <c r="H45" s="61"/>
+      <c r="E45" s="65"/>
+      <c r="F45" s="65"/>
+      <c r="G45" s="65"/>
+      <c r="H45" s="66"/>
     </row>
     <row r="46" spans="1:8" ht="9" customHeight="1">
-      <c r="A46" s="57"/>
+      <c r="A46" s="62"/>
       <c r="B46" s="20"/>
       <c r="C46" s="20"/>
       <c r="D46" s="21"/>
-      <c r="E46" s="60"/>
-      <c r="F46" s="60"/>
-      <c r="G46" s="60"/>
-      <c r="H46" s="61"/>
+      <c r="E46" s="65"/>
+      <c r="F46" s="65"/>
+      <c r="G46" s="65"/>
+      <c r="H46" s="66"/>
     </row>
     <row r="47" spans="1:8" ht="9" customHeight="1">
-      <c r="A47" s="57"/>
+      <c r="A47" s="62"/>
       <c r="B47" s="20"/>
       <c r="C47" s="20"/>
       <c r="D47" s="22"/>
-      <c r="E47" s="62"/>
-      <c r="F47" s="62"/>
-      <c r="G47" s="62"/>
-      <c r="H47" s="63"/>
+      <c r="E47" s="67"/>
+      <c r="F47" s="67"/>
+      <c r="G47" s="67"/>
+      <c r="H47" s="68"/>
     </row>
     <row r="48" spans="1:8" ht="9" customHeight="1">
-      <c r="A48" s="57"/>
+      <c r="A48" s="62"/>
       <c r="B48" s="23"/>
       <c r="C48" s="23"/>
       <c r="D48" s="22"/>
-      <c r="E48" s="62"/>
-      <c r="F48" s="62"/>
-      <c r="G48" s="62"/>
-      <c r="H48" s="63"/>
+      <c r="E48" s="67"/>
+      <c r="F48" s="67"/>
+      <c r="G48" s="67"/>
+      <c r="H48" s="68"/>
     </row>
     <row r="49" spans="1:8" ht="9" customHeight="1">
-      <c r="A49" s="64" t="s">
+      <c r="A49" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="B49" s="65"/>
-      <c r="C49" s="66"/>
-      <c r="D49" s="73" t="s">
+      <c r="B49" s="47"/>
+      <c r="C49" s="48"/>
+      <c r="D49" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="E49" s="73"/>
-      <c r="F49" s="73"/>
-      <c r="G49" s="73"/>
-      <c r="H49" s="74"/>
+      <c r="E49" s="55"/>
+      <c r="F49" s="55"/>
+      <c r="G49" s="55"/>
+      <c r="H49" s="56"/>
     </row>
     <row r="50" spans="1:8" ht="9" customHeight="1">
-      <c r="A50" s="67"/>
-      <c r="B50" s="68"/>
-      <c r="C50" s="69"/>
-      <c r="D50" s="24" t="s">
+      <c r="A50" s="49"/>
+      <c r="B50" s="50"/>
+      <c r="C50" s="51"/>
+      <c r="D50" s="93" t="s">
+        <v>59</v>
+      </c>
+      <c r="E50" s="93"/>
+      <c r="F50" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="E50" s="44"/>
-      <c r="F50" s="44"/>
-      <c r="G50" s="75"/>
-      <c r="H50" s="25" t="s">
+      <c r="G50" s="93"/>
+      <c r="H50" s="24" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="9" customHeight="1">
-      <c r="A51" s="67"/>
-      <c r="B51" s="68"/>
-      <c r="C51" s="69"/>
-      <c r="D51" s="76"/>
-      <c r="E51" s="77"/>
-      <c r="F51" s="77"/>
-      <c r="G51" s="78"/>
-      <c r="H51" s="26"/>
+      <c r="A51" s="49"/>
+      <c r="B51" s="50"/>
+      <c r="C51" s="51"/>
+      <c r="D51" s="67"/>
+      <c r="E51" s="67"/>
+      <c r="F51" s="93"/>
+      <c r="G51" s="93"/>
+      <c r="H51" s="25"/>
     </row>
     <row r="52" spans="1:8" ht="9" customHeight="1">
-      <c r="A52" s="67"/>
-      <c r="B52" s="68"/>
-      <c r="C52" s="69"/>
-      <c r="D52" s="76"/>
-      <c r="E52" s="77"/>
-      <c r="F52" s="77"/>
-      <c r="G52" s="78"/>
-      <c r="H52" s="26"/>
+      <c r="A52" s="49"/>
+      <c r="B52" s="50"/>
+      <c r="C52" s="51"/>
+      <c r="D52" s="67"/>
+      <c r="E52" s="67"/>
+      <c r="F52" s="93"/>
+      <c r="G52" s="93"/>
+      <c r="H52" s="25"/>
     </row>
     <row r="53" spans="1:8" ht="9" customHeight="1">
-      <c r="A53" s="67"/>
-      <c r="B53" s="68"/>
-      <c r="C53" s="69"/>
-      <c r="D53" s="76"/>
-      <c r="E53" s="77"/>
-      <c r="F53" s="77"/>
-      <c r="G53" s="78"/>
-      <c r="H53" s="26"/>
+      <c r="A53" s="49"/>
+      <c r="B53" s="50"/>
+      <c r="C53" s="51"/>
+      <c r="D53" s="67"/>
+      <c r="E53" s="67"/>
+      <c r="F53" s="93"/>
+      <c r="G53" s="93"/>
+      <c r="H53" s="25"/>
     </row>
     <row r="54" spans="1:8" ht="9" customHeight="1">
-      <c r="A54" s="67"/>
-      <c r="B54" s="68"/>
-      <c r="C54" s="69"/>
-      <c r="D54" s="76"/>
-      <c r="E54" s="77"/>
-      <c r="F54" s="77"/>
-      <c r="G54" s="78"/>
-      <c r="H54" s="26"/>
+      <c r="A54" s="49"/>
+      <c r="B54" s="50"/>
+      <c r="C54" s="51"/>
+      <c r="D54" s="67"/>
+      <c r="E54" s="67"/>
+      <c r="F54" s="93"/>
+      <c r="G54" s="93"/>
+      <c r="H54" s="25"/>
     </row>
     <row r="55" spans="1:8" ht="9" customHeight="1">
-      <c r="A55" s="67"/>
-      <c r="B55" s="68"/>
-      <c r="C55" s="69"/>
-      <c r="D55" s="76"/>
-      <c r="E55" s="77"/>
-      <c r="F55" s="77"/>
-      <c r="G55" s="78"/>
-      <c r="H55" s="26"/>
+      <c r="A55" s="49"/>
+      <c r="B55" s="50"/>
+      <c r="C55" s="51"/>
+      <c r="D55" s="67"/>
+      <c r="E55" s="67"/>
+      <c r="F55" s="93"/>
+      <c r="G55" s="93"/>
+      <c r="H55" s="25"/>
     </row>
     <row r="56" spans="1:8" ht="9" customHeight="1">
-      <c r="A56" s="67"/>
-      <c r="B56" s="68"/>
-      <c r="C56" s="69"/>
-      <c r="D56" s="79"/>
-      <c r="E56" s="80"/>
-      <c r="F56" s="80"/>
-      <c r="G56" s="78"/>
-      <c r="H56" s="26"/>
+      <c r="A56" s="49"/>
+      <c r="B56" s="50"/>
+      <c r="C56" s="51"/>
+      <c r="D56" s="67"/>
+      <c r="E56" s="67"/>
+      <c r="F56" s="93"/>
+      <c r="G56" s="93"/>
+      <c r="H56" s="25"/>
     </row>
     <row r="57" spans="1:8" ht="9" customHeight="1">
-      <c r="A57" s="67"/>
-      <c r="B57" s="68"/>
-      <c r="C57" s="69"/>
-      <c r="D57" s="81" t="s">
+      <c r="A57" s="49"/>
+      <c r="B57" s="50"/>
+      <c r="C57" s="51"/>
+      <c r="D57" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="E57" s="82"/>
-      <c r="F57" s="83"/>
-      <c r="G57" s="85"/>
-      <c r="H57" s="86"/>
+      <c r="E57" s="59"/>
+      <c r="F57" s="60"/>
+      <c r="G57" s="31"/>
+      <c r="H57" s="32"/>
     </row>
     <row r="58" spans="1:8" ht="9" customHeight="1">
-      <c r="A58" s="67"/>
-      <c r="B58" s="68"/>
-      <c r="C58" s="69"/>
-      <c r="D58" s="89" t="s">
+      <c r="A58" s="49"/>
+      <c r="B58" s="50"/>
+      <c r="C58" s="51"/>
+      <c r="D58" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="E58" s="90"/>
-      <c r="F58" s="91"/>
-      <c r="G58" s="87"/>
-      <c r="H58" s="88"/>
+      <c r="E58" s="36"/>
+      <c r="F58" s="37"/>
+      <c r="G58" s="33"/>
+      <c r="H58" s="34"/>
     </row>
     <row r="59" spans="1:8" ht="9" customHeight="1">
-      <c r="A59" s="67"/>
-      <c r="B59" s="68"/>
-      <c r="C59" s="69"/>
-      <c r="D59" s="92" t="s">
+      <c r="A59" s="49"/>
+      <c r="B59" s="50"/>
+      <c r="C59" s="51"/>
+      <c r="D59" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="E59" s="93"/>
-      <c r="F59" s="94"/>
-      <c r="G59" s="85"/>
-      <c r="H59" s="86"/>
+      <c r="E59" s="39"/>
+      <c r="F59" s="40"/>
+      <c r="G59" s="31"/>
+      <c r="H59" s="32"/>
     </row>
     <row r="60" spans="1:8" ht="9" customHeight="1">
-      <c r="A60" s="67"/>
-      <c r="B60" s="68"/>
-      <c r="C60" s="69"/>
-      <c r="D60" s="89" t="s">
+      <c r="A60" s="49"/>
+      <c r="B60" s="50"/>
+      <c r="C60" s="51"/>
+      <c r="D60" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="E60" s="90"/>
-      <c r="F60" s="91"/>
-      <c r="G60" s="87"/>
-      <c r="H60" s="88"/>
+      <c r="E60" s="36"/>
+      <c r="F60" s="37"/>
+      <c r="G60" s="33"/>
+      <c r="H60" s="34"/>
     </row>
     <row r="61" spans="1:8" ht="9" customHeight="1">
-      <c r="A61" s="67"/>
-      <c r="B61" s="68"/>
-      <c r="C61" s="69"/>
-      <c r="D61" s="93" t="s">
+      <c r="A61" s="49"/>
+      <c r="B61" s="50"/>
+      <c r="C61" s="51"/>
+      <c r="D61" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E61" s="93"/>
-      <c r="F61" s="94"/>
-      <c r="G61" s="85"/>
-      <c r="H61" s="86"/>
+      <c r="E61" s="39"/>
+      <c r="F61" s="40"/>
+      <c r="G61" s="31"/>
+      <c r="H61" s="32"/>
     </row>
     <row r="62" spans="1:8" ht="9" customHeight="1" thickBot="1">
-      <c r="A62" s="70"/>
-      <c r="B62" s="71"/>
-      <c r="C62" s="72"/>
-      <c r="D62" s="97" t="s">
+      <c r="A62" s="52"/>
+      <c r="B62" s="53"/>
+      <c r="C62" s="54"/>
+      <c r="D62" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="E62" s="98"/>
-      <c r="F62" s="99"/>
-      <c r="G62" s="95"/>
-      <c r="H62" s="96"/>
+      <c r="E62" s="44"/>
+      <c r="F62" s="45"/>
+      <c r="G62" s="41"/>
+      <c r="H62" s="42"/>
     </row>
     <row r="63" spans="1:8" ht="9" customHeight="1" thickTop="1">
-      <c r="F63" s="84" t="s">
+      <c r="F63" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="G63" s="84"/>
-      <c r="H63" s="84"/>
+      <c r="G63" s="30"/>
+      <c r="H63" s="30"/>
     </row>
     <row r="64" spans="1:8" ht="9" customHeight="1">
       <c r="A64"/>
@@ -2150,132 +2124,34 @@
       <c r="G64"/>
       <c r="H64"/>
     </row>
-    <row r="65" spans="1:8">
-      <c r="A65"/>
-      <c r="B65"/>
-      <c r="C65"/>
-      <c r="D65"/>
-      <c r="E65"/>
-      <c r="F65"/>
-      <c r="G65"/>
-      <c r="H65"/>
-    </row>
-    <row r="66" spans="1:8">
-      <c r="A66"/>
-      <c r="B66"/>
-      <c r="C66"/>
-      <c r="D66"/>
-      <c r="E66"/>
-      <c r="F66"/>
-      <c r="G66"/>
-      <c r="H66"/>
-    </row>
-    <row r="67" spans="1:8">
-      <c r="A67"/>
-      <c r="B67"/>
-      <c r="C67"/>
-      <c r="D67"/>
-      <c r="E67"/>
-      <c r="F67"/>
-      <c r="G67"/>
-      <c r="H67"/>
-    </row>
-    <row r="68" spans="1:8">
-      <c r="A68"/>
-      <c r="B68"/>
-      <c r="C68"/>
-      <c r="D68"/>
-      <c r="E68"/>
-      <c r="F68"/>
-      <c r="G68"/>
-      <c r="H68"/>
-    </row>
-    <row r="69" spans="1:8">
-      <c r="A69"/>
-      <c r="B69"/>
-      <c r="C69"/>
-      <c r="D69"/>
-      <c r="E69"/>
-      <c r="F69"/>
-      <c r="G69"/>
-      <c r="H69"/>
-    </row>
-    <row r="70" spans="1:8">
-      <c r="A70"/>
-      <c r="B70"/>
-      <c r="C70"/>
-      <c r="D70"/>
-      <c r="E70"/>
-      <c r="F70"/>
-      <c r="G70"/>
-      <c r="H70"/>
-    </row>
-    <row r="71" spans="1:8">
-      <c r="A71"/>
-      <c r="B71"/>
-      <c r="C71"/>
-      <c r="D71"/>
-      <c r="E71"/>
-      <c r="F71"/>
-      <c r="G71"/>
-      <c r="H71"/>
-    </row>
+    <row r="65" customFormat="1"/>
+    <row r="66" customFormat="1"/>
+    <row r="67" customFormat="1"/>
+    <row r="68" customFormat="1"/>
+    <row r="69" customFormat="1"/>
+    <row r="70" customFormat="1"/>
+    <row r="71" customFormat="1"/>
   </sheetData>
-  <mergeCells count="79">
-    <mergeCell ref="F63:H63"/>
-    <mergeCell ref="G57:H58"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="G59:H60"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="G61:H62"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="A49:C62"/>
-    <mergeCell ref="D49:H49"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="D51:G51"/>
-    <mergeCell ref="D52:G52"/>
-    <mergeCell ref="D53:G53"/>
-    <mergeCell ref="D54:G54"/>
-    <mergeCell ref="D55:G55"/>
-    <mergeCell ref="D56:G56"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="A44:A48"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="A39:A43"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="A33:A38"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="A26:A32"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="A19:A25"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E25:H25"/>
+  <mergeCells count="86">
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F5:H5"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="E7:H7"/>
     <mergeCell ref="A8:A18"/>
@@ -2290,17 +2166,59 @@
     <mergeCell ref="E16:H16"/>
     <mergeCell ref="E17:H17"/>
     <mergeCell ref="E18:H18"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="A19:A25"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="A26:A32"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="A33:A38"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="A39:A43"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="A44:A48"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="A49:C62"/>
+    <mergeCell ref="D49:H49"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="F63:H63"/>
+    <mergeCell ref="G57:H58"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="G59:H60"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="G61:H62"/>
+    <mergeCell ref="D62:F62"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.195138888888889" bottom="0" header="0" footer="0"/>

--- a/public/assets/templates/maintenance/electrical.xlsx
+++ b/public/assets/templates/maintenance/electrical.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D425089-7679-486B-9C6F-93017B77A7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C2056B3-2DE4-4E77-B8D1-3729BA8E0311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{1839BE4E-8ABA-4E0E-BDE7-D891D69ECECB}"/>
   </bookViews>
@@ -174,18 +174,9 @@
     <t>Teknisi</t>
   </si>
   <si>
-    <t>Diketahui : Miftah Hasan Fuadi</t>
-  </si>
-  <si>
     <t>Staff Engineering</t>
   </si>
   <si>
-    <t>Diterima</t>
-  </si>
-  <si>
-    <t>Staff User</t>
-  </si>
-  <si>
     <t>FRM/EUT/01/009/007-02</t>
   </si>
   <si>
@@ -205,13 +196,22 @@
   </si>
   <si>
     <t>MID</t>
+  </si>
+  <si>
+    <t>Diketahui : Reja Firmansyah</t>
+  </si>
+  <si>
+    <t>Supervisor Engineering</t>
+  </si>
+  <si>
+    <t>Diperiksa : Miftah Hasan Fuadi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -220,69 +220,83 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="7"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="7"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="7"/>
       <color indexed="8"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="7"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="7"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -290,7 +304,7 @@
       <sz val="7"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -628,15 +642,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color auto="1"/>
       </left>
@@ -689,299 +694,315 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{6FB050D8-96A7-4DFC-AAFC-0DA1EAD6D8F2}"/>
+    <cellStyle name="Normal 3" xfId="3" xr:uid="{B17FA85C-0217-4649-BF72-B42B57533D1A}"/>
     <cellStyle name="Normal_Inspection Test Plan" xfId="1" xr:uid="{9BC175D4-98DF-45A6-8EC1-D792C7BCAE7B}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1361,82 +1382,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" thickTop="1">
-      <c r="A1" s="85"/>
-      <c r="B1" s="86"/>
-      <c r="C1" s="89" t="s">
+      <c r="A1" s="84"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
-      <c r="H1" s="90"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="89"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="87"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="91" t="s">
+      <c r="A2" s="86"/>
+      <c r="B2" s="87"/>
+      <c r="C2" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
-      <c r="H2" s="92"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="91"/>
     </row>
     <row r="3" spans="1:8" ht="10.25" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="82" t="s">
+      <c r="D3" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="82"/>
-      <c r="F3" s="83" t="s">
+      <c r="E3" s="81"/>
+      <c r="F3" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="83"/>
-      <c r="H3" s="84"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="83"/>
     </row>
     <row r="4" spans="1:8" ht="10.25" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="82" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="82"/>
-      <c r="F4" s="83" t="s">
+      <c r="D4" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="81"/>
+      <c r="F4" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="83"/>
-      <c r="H4" s="84"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="83"/>
     </row>
     <row r="5" spans="1:8" ht="10.25" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="82" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="82"/>
-      <c r="F5" s="83" t="s">
+      <c r="D5" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="81"/>
+      <c r="F5" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="G5" s="83"/>
-      <c r="H5" s="84"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="83"/>
     </row>
     <row r="6" spans="1:8" ht="10.25" customHeight="1">
       <c r="A6" s="1" t="s">
@@ -1446,36 +1467,36 @@
         <v>2</v>
       </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="82" t="s">
+      <c r="D6" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="82"/>
-      <c r="F6" s="83" t="s">
+      <c r="E6" s="81"/>
+      <c r="F6" s="82" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="83"/>
-      <c r="H6" s="84"/>
+      <c r="G6" s="82"/>
+      <c r="H6" s="83"/>
     </row>
     <row r="7" spans="1:8" s="5" customFormat="1" ht="10.25" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="79" t="s">
+      <c r="B7" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="79"/>
+      <c r="C7" s="77"/>
       <c r="D7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="80" t="s">
+      <c r="E7" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="81"/>
+      <c r="F7" s="79"/>
+      <c r="G7" s="79"/>
+      <c r="H7" s="80"/>
     </row>
     <row r="8" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A8" s="76" t="s">
+      <c r="A8" s="74" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="6"/>
@@ -1483,130 +1504,130 @@
         <v>12</v>
       </c>
       <c r="D8" s="27"/>
-      <c r="E8" s="72"/>
-      <c r="F8" s="73"/>
-      <c r="G8" s="73"/>
-      <c r="H8" s="74"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="71"/>
+      <c r="H8" s="72"/>
     </row>
     <row r="9" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A9" s="77"/>
+      <c r="A9" s="75"/>
       <c r="B9" s="6"/>
       <c r="C9" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="27"/>
-      <c r="E9" s="72"/>
-      <c r="F9" s="73"/>
-      <c r="G9" s="73"/>
-      <c r="H9" s="74"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="72"/>
     </row>
     <row r="10" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A10" s="77"/>
+      <c r="A10" s="75"/>
       <c r="B10" s="6"/>
       <c r="C10" s="7" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="27"/>
-      <c r="E10" s="72"/>
-      <c r="F10" s="73"/>
-      <c r="G10" s="73"/>
-      <c r="H10" s="74"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="72"/>
     </row>
     <row r="11" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A11" s="77"/>
+      <c r="A11" s="75"/>
       <c r="B11" s="6"/>
       <c r="C11" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D11" s="27"/>
-      <c r="E11" s="72"/>
-      <c r="F11" s="73"/>
-      <c r="G11" s="73"/>
-      <c r="H11" s="74"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="72"/>
     </row>
     <row r="12" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A12" s="77"/>
+      <c r="A12" s="75"/>
       <c r="B12" s="6"/>
       <c r="C12" s="7" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="27"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="73"/>
-      <c r="H12" s="74"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="71"/>
+      <c r="H12" s="72"/>
     </row>
     <row r="13" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A13" s="77"/>
+      <c r="A13" s="75"/>
       <c r="B13" s="6"/>
       <c r="C13" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D13" s="27"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="73"/>
-      <c r="G13" s="73"/>
-      <c r="H13" s="74"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="72"/>
     </row>
     <row r="14" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A14" s="77"/>
+      <c r="A14" s="75"/>
       <c r="B14" s="6"/>
       <c r="C14" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="27"/>
-      <c r="E14" s="72"/>
-      <c r="F14" s="73"/>
-      <c r="G14" s="73"/>
-      <c r="H14" s="74"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="72"/>
     </row>
     <row r="15" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A15" s="77"/>
+      <c r="A15" s="75"/>
       <c r="B15" s="6"/>
       <c r="C15" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D15" s="27"/>
-      <c r="E15" s="72"/>
-      <c r="F15" s="73"/>
-      <c r="G15" s="73"/>
-      <c r="H15" s="74"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="72"/>
     </row>
     <row r="16" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A16" s="77"/>
+      <c r="A16" s="75"/>
       <c r="B16" s="6"/>
       <c r="C16" s="10" t="s">
         <v>20</v>
       </c>
       <c r="D16" s="27"/>
-      <c r="E16" s="72"/>
-      <c r="F16" s="73"/>
-      <c r="G16" s="73"/>
-      <c r="H16" s="74"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="72"/>
     </row>
     <row r="17" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A17" s="77"/>
+      <c r="A17" s="75"/>
       <c r="B17" s="6"/>
       <c r="C17" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D17" s="27"/>
-      <c r="E17" s="72"/>
-      <c r="F17" s="73"/>
-      <c r="G17" s="73"/>
-      <c r="H17" s="74"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="72"/>
     </row>
     <row r="18" spans="1:10" s="10" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A18" s="78"/>
+      <c r="A18" s="76"/>
       <c r="B18" s="6"/>
       <c r="D18" s="27"/>
-      <c r="E18" s="72"/>
-      <c r="F18" s="73"/>
-      <c r="G18" s="73"/>
-      <c r="H18" s="74"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="72"/>
     </row>
     <row r="19" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A19" s="76" t="s">
+      <c r="A19" s="74" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="6"/>
@@ -1614,81 +1635,81 @@
         <v>23</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="72"/>
-      <c r="F19" s="73"/>
-      <c r="G19" s="73"/>
-      <c r="H19" s="74"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="72"/>
     </row>
     <row r="20" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A20" s="77"/>
+      <c r="A20" s="75"/>
       <c r="B20" s="6"/>
       <c r="C20" s="7" t="s">
         <v>24</v>
       </c>
       <c r="D20" s="27"/>
-      <c r="E20" s="72"/>
-      <c r="F20" s="73"/>
-      <c r="G20" s="73"/>
-      <c r="H20" s="74"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="72"/>
     </row>
     <row r="21" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A21" s="77"/>
+      <c r="A21" s="75"/>
       <c r="B21" s="6"/>
       <c r="C21" s="7" t="s">
         <v>25</v>
       </c>
       <c r="D21" s="27"/>
-      <c r="E21" s="72"/>
-      <c r="F21" s="73"/>
-      <c r="G21" s="73"/>
-      <c r="H21" s="74"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="72"/>
     </row>
     <row r="22" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A22" s="77"/>
+      <c r="A22" s="75"/>
       <c r="B22" s="6"/>
       <c r="C22" s="11" t="s">
         <v>26</v>
       </c>
       <c r="D22" s="27"/>
-      <c r="E22" s="72"/>
-      <c r="F22" s="73"/>
-      <c r="G22" s="73"/>
-      <c r="H22" s="74"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="72"/>
     </row>
     <row r="23" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A23" s="77"/>
+      <c r="A23" s="75"/>
       <c r="B23" s="6"/>
       <c r="C23" s="12" t="s">
         <v>27</v>
       </c>
       <c r="D23" s="27"/>
-      <c r="E23" s="72"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="74"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="72"/>
     </row>
     <row r="24" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A24" s="77"/>
+      <c r="A24" s="75"/>
       <c r="B24" s="6"/>
       <c r="C24" s="7"/>
       <c r="D24" s="27"/>
-      <c r="E24" s="72"/>
-      <c r="F24" s="73"/>
-      <c r="G24" s="73"/>
-      <c r="H24" s="74"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="72"/>
     </row>
     <row r="25" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A25" s="78"/>
+      <c r="A25" s="76"/>
       <c r="B25" s="6"/>
       <c r="C25" s="13"/>
       <c r="D25" s="27"/>
-      <c r="E25" s="72"/>
-      <c r="F25" s="73"/>
-      <c r="G25" s="73"/>
-      <c r="H25" s="74"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="72"/>
     </row>
     <row r="26" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A26" s="75" t="s">
+      <c r="A26" s="73" t="s">
         <v>28</v>
       </c>
       <c r="B26" s="6"/>
@@ -1696,81 +1717,81 @@
         <v>29</v>
       </c>
       <c r="D26" s="27"/>
-      <c r="E26" s="72"/>
-      <c r="F26" s="73"/>
-      <c r="G26" s="73"/>
-      <c r="H26" s="74"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="72"/>
     </row>
     <row r="27" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A27" s="75"/>
+      <c r="A27" s="73"/>
       <c r="B27" s="6"/>
       <c r="C27" s="14" t="s">
         <v>30</v>
       </c>
       <c r="D27" s="27"/>
-      <c r="E27" s="72"/>
-      <c r="F27" s="73"/>
-      <c r="G27" s="73"/>
-      <c r="H27" s="74"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="72"/>
       <c r="J27" s="15"/>
     </row>
     <row r="28" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A28" s="75"/>
+      <c r="A28" s="73"/>
       <c r="B28" s="6"/>
       <c r="C28" s="14" t="s">
         <v>31</v>
       </c>
       <c r="D28" s="27"/>
-      <c r="E28" s="72"/>
-      <c r="F28" s="73"/>
-      <c r="G28" s="73"/>
-      <c r="H28" s="74"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="72"/>
     </row>
     <row r="29" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A29" s="75"/>
+      <c r="A29" s="73"/>
       <c r="B29" s="6"/>
       <c r="C29" s="14" t="s">
         <v>32</v>
       </c>
       <c r="D29" s="27"/>
-      <c r="E29" s="72"/>
-      <c r="F29" s="73"/>
-      <c r="G29" s="73"/>
-      <c r="H29" s="74"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="72"/>
     </row>
     <row r="30" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A30" s="75"/>
+      <c r="A30" s="73"/>
       <c r="B30" s="6"/>
       <c r="C30" s="14" t="s">
         <v>33</v>
       </c>
       <c r="D30" s="27"/>
-      <c r="E30" s="72"/>
-      <c r="F30" s="73"/>
-      <c r="G30" s="73"/>
-      <c r="H30" s="74"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="72"/>
     </row>
     <row r="31" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A31" s="75"/>
+      <c r="A31" s="73"/>
       <c r="B31" s="6"/>
       <c r="C31" s="14"/>
       <c r="D31" s="27"/>
-      <c r="E31" s="72"/>
-      <c r="F31" s="73"/>
-      <c r="G31" s="73"/>
-      <c r="H31" s="74"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="72"/>
     </row>
     <row r="32" spans="1:10" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A32" s="75"/>
+      <c r="A32" s="73"/>
       <c r="B32" s="6"/>
       <c r="D32" s="27"/>
-      <c r="E32" s="72"/>
-      <c r="F32" s="73"/>
-      <c r="G32" s="73"/>
-      <c r="H32" s="74"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="72"/>
     </row>
     <row r="33" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A33" s="69" t="s">
+      <c r="A33" s="67" t="s">
         <v>34</v>
       </c>
       <c r="B33" s="6"/>
@@ -1778,68 +1799,68 @@
         <v>35</v>
       </c>
       <c r="D33" s="27"/>
-      <c r="E33" s="72"/>
-      <c r="F33" s="73"/>
-      <c r="G33" s="73"/>
-      <c r="H33" s="74"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="72"/>
     </row>
     <row r="34" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A34" s="70"/>
+      <c r="A34" s="68"/>
       <c r="B34" s="6"/>
       <c r="C34" s="16" t="s">
         <v>36</v>
       </c>
       <c r="D34" s="27"/>
-      <c r="E34" s="72"/>
-      <c r="F34" s="73"/>
-      <c r="G34" s="73"/>
-      <c r="H34" s="74"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="72"/>
     </row>
     <row r="35" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A35" s="70"/>
+      <c r="A35" s="68"/>
       <c r="B35" s="6"/>
       <c r="C35" s="7" t="s">
         <v>37</v>
       </c>
       <c r="D35" s="27"/>
-      <c r="E35" s="72"/>
-      <c r="F35" s="73"/>
-      <c r="G35" s="73"/>
-      <c r="H35" s="74"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="72"/>
     </row>
     <row r="36" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A36" s="70"/>
+      <c r="A36" s="68"/>
       <c r="B36" s="6"/>
       <c r="C36" s="7" t="s">
         <v>38</v>
       </c>
       <c r="D36" s="27"/>
-      <c r="E36" s="72"/>
-      <c r="F36" s="73"/>
-      <c r="G36" s="73"/>
-      <c r="H36" s="74"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="72"/>
     </row>
     <row r="37" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A37" s="70"/>
+      <c r="A37" s="68"/>
       <c r="B37" s="6"/>
       <c r="C37" s="7"/>
       <c r="D37" s="27"/>
-      <c r="E37" s="72"/>
-      <c r="F37" s="73"/>
-      <c r="G37" s="73"/>
-      <c r="H37" s="74"/>
+      <c r="E37" s="70"/>
+      <c r="F37" s="71"/>
+      <c r="G37" s="71"/>
+      <c r="H37" s="72"/>
     </row>
     <row r="38" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A38" s="71"/>
+      <c r="A38" s="69"/>
       <c r="B38" s="6"/>
       <c r="D38" s="27"/>
-      <c r="E38" s="72"/>
-      <c r="F38" s="73"/>
-      <c r="G38" s="73"/>
-      <c r="H38" s="74"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="72"/>
     </row>
     <row r="39" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A39" s="69" t="s">
+      <c r="A39" s="67" t="s">
         <v>39</v>
       </c>
       <c r="B39" s="6"/>
@@ -1847,210 +1868,210 @@
         <v>40</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="72"/>
-      <c r="F39" s="73"/>
-      <c r="G39" s="73"/>
-      <c r="H39" s="74"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="72"/>
     </row>
     <row r="40" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A40" s="70"/>
+      <c r="A40" s="68"/>
       <c r="B40" s="6"/>
       <c r="C40" s="7" t="s">
         <v>41</v>
       </c>
       <c r="D40" s="27"/>
-      <c r="E40" s="72"/>
-      <c r="F40" s="73"/>
-      <c r="G40" s="73"/>
-      <c r="H40" s="74"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="71"/>
+      <c r="G40" s="71"/>
+      <c r="H40" s="72"/>
     </row>
     <row r="41" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A41" s="70"/>
+      <c r="A41" s="68"/>
       <c r="B41" s="6"/>
       <c r="C41" s="17" t="s">
         <v>42</v>
       </c>
       <c r="D41" s="27"/>
-      <c r="E41" s="72"/>
-      <c r="F41" s="73"/>
-      <c r="G41" s="73"/>
-      <c r="H41" s="74"/>
+      <c r="E41" s="70"/>
+      <c r="F41" s="71"/>
+      <c r="G41" s="71"/>
+      <c r="H41" s="72"/>
     </row>
     <row r="42" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A42" s="70"/>
+      <c r="A42" s="68"/>
       <c r="B42" s="6"/>
       <c r="C42" s="7"/>
       <c r="D42" s="27"/>
-      <c r="E42" s="72"/>
-      <c r="F42" s="73"/>
-      <c r="G42" s="73"/>
-      <c r="H42" s="74"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="72"/>
     </row>
     <row r="43" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A43" s="71"/>
+      <c r="A43" s="69"/>
       <c r="B43" s="18"/>
       <c r="D43" s="28"/>
-      <c r="E43" s="72"/>
-      <c r="F43" s="73"/>
-      <c r="G43" s="73"/>
-      <c r="H43" s="74"/>
+      <c r="E43" s="70"/>
+      <c r="F43" s="71"/>
+      <c r="G43" s="71"/>
+      <c r="H43" s="72"/>
     </row>
     <row r="44" spans="1:8" s="8" customFormat="1" ht="10.25" customHeight="1">
-      <c r="A44" s="61"/>
+      <c r="A44" s="59"/>
       <c r="B44" s="19"/>
       <c r="C44" s="19"/>
       <c r="D44" s="29"/>
-      <c r="E44" s="63"/>
-      <c r="F44" s="63"/>
-      <c r="G44" s="63"/>
-      <c r="H44" s="64"/>
+      <c r="E44" s="61"/>
+      <c r="F44" s="61"/>
+      <c r="G44" s="61"/>
+      <c r="H44" s="62"/>
     </row>
     <row r="45" spans="1:8" ht="9" customHeight="1">
-      <c r="A45" s="62"/>
+      <c r="A45" s="60"/>
       <c r="B45" s="20"/>
       <c r="C45" s="20"/>
       <c r="D45" s="21"/>
-      <c r="E45" s="65"/>
-      <c r="F45" s="65"/>
-      <c r="G45" s="65"/>
-      <c r="H45" s="66"/>
+      <c r="E45" s="63"/>
+      <c r="F45" s="63"/>
+      <c r="G45" s="63"/>
+      <c r="H45" s="64"/>
     </row>
     <row r="46" spans="1:8" ht="9" customHeight="1">
-      <c r="A46" s="62"/>
+      <c r="A46" s="60"/>
       <c r="B46" s="20"/>
       <c r="C46" s="20"/>
       <c r="D46" s="21"/>
-      <c r="E46" s="65"/>
-      <c r="F46" s="65"/>
-      <c r="G46" s="65"/>
-      <c r="H46" s="66"/>
+      <c r="E46" s="63"/>
+      <c r="F46" s="63"/>
+      <c r="G46" s="63"/>
+      <c r="H46" s="64"/>
     </row>
     <row r="47" spans="1:8" ht="9" customHeight="1">
-      <c r="A47" s="62"/>
+      <c r="A47" s="60"/>
       <c r="B47" s="20"/>
       <c r="C47" s="20"/>
       <c r="D47" s="22"/>
-      <c r="E47" s="67"/>
-      <c r="F47" s="67"/>
-      <c r="G47" s="67"/>
-      <c r="H47" s="68"/>
+      <c r="E47" s="65"/>
+      <c r="F47" s="65"/>
+      <c r="G47" s="65"/>
+      <c r="H47" s="66"/>
     </row>
     <row r="48" spans="1:8" ht="9" customHeight="1">
-      <c r="A48" s="62"/>
+      <c r="A48" s="60"/>
       <c r="B48" s="23"/>
       <c r="C48" s="23"/>
       <c r="D48" s="22"/>
-      <c r="E48" s="67"/>
-      <c r="F48" s="67"/>
-      <c r="G48" s="67"/>
-      <c r="H48" s="68"/>
+      <c r="E48" s="65"/>
+      <c r="F48" s="65"/>
+      <c r="G48" s="65"/>
+      <c r="H48" s="66"/>
     </row>
     <row r="49" spans="1:8" ht="9" customHeight="1">
-      <c r="A49" s="46" t="s">
+      <c r="A49" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="B49" s="47"/>
-      <c r="C49" s="48"/>
-      <c r="D49" s="55" t="s">
+      <c r="B49" s="45"/>
+      <c r="C49" s="46"/>
+      <c r="D49" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="E49" s="55"/>
-      <c r="F49" s="55"/>
-      <c r="G49" s="55"/>
-      <c r="H49" s="56"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="53"/>
+      <c r="G49" s="53"/>
+      <c r="H49" s="54"/>
     </row>
     <row r="50" spans="1:8" ht="9" customHeight="1">
-      <c r="A50" s="49"/>
-      <c r="B50" s="50"/>
-      <c r="C50" s="51"/>
-      <c r="D50" s="93" t="s">
-        <v>59</v>
-      </c>
-      <c r="E50" s="93"/>
-      <c r="F50" s="93" t="s">
+      <c r="A50" s="47"/>
+      <c r="B50" s="48"/>
+      <c r="C50" s="49"/>
+      <c r="D50" s="58" t="s">
+        <v>56</v>
+      </c>
+      <c r="E50" s="58"/>
+      <c r="F50" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="G50" s="93"/>
+      <c r="G50" s="58"/>
       <c r="H50" s="24" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="9" customHeight="1">
-      <c r="A51" s="49"/>
-      <c r="B51" s="50"/>
-      <c r="C51" s="51"/>
-      <c r="D51" s="67"/>
-      <c r="E51" s="67"/>
-      <c r="F51" s="93"/>
-      <c r="G51" s="93"/>
+      <c r="A51" s="47"/>
+      <c r="B51" s="48"/>
+      <c r="C51" s="49"/>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="58"/>
+      <c r="G51" s="58"/>
       <c r="H51" s="25"/>
     </row>
     <row r="52" spans="1:8" ht="9" customHeight="1">
-      <c r="A52" s="49"/>
-      <c r="B52" s="50"/>
-      <c r="C52" s="51"/>
-      <c r="D52" s="67"/>
-      <c r="E52" s="67"/>
-      <c r="F52" s="93"/>
-      <c r="G52" s="93"/>
+      <c r="A52" s="47"/>
+      <c r="B52" s="48"/>
+      <c r="C52" s="49"/>
+      <c r="D52" s="65"/>
+      <c r="E52" s="65"/>
+      <c r="F52" s="58"/>
+      <c r="G52" s="58"/>
       <c r="H52" s="25"/>
     </row>
     <row r="53" spans="1:8" ht="9" customHeight="1">
-      <c r="A53" s="49"/>
-      <c r="B53" s="50"/>
-      <c r="C53" s="51"/>
-      <c r="D53" s="67"/>
-      <c r="E53" s="67"/>
-      <c r="F53" s="93"/>
-      <c r="G53" s="93"/>
+      <c r="A53" s="47"/>
+      <c r="B53" s="48"/>
+      <c r="C53" s="49"/>
+      <c r="D53" s="65"/>
+      <c r="E53" s="65"/>
+      <c r="F53" s="58"/>
+      <c r="G53" s="58"/>
       <c r="H53" s="25"/>
     </row>
     <row r="54" spans="1:8" ht="9" customHeight="1">
-      <c r="A54" s="49"/>
-      <c r="B54" s="50"/>
-      <c r="C54" s="51"/>
-      <c r="D54" s="67"/>
-      <c r="E54" s="67"/>
-      <c r="F54" s="93"/>
-      <c r="G54" s="93"/>
+      <c r="A54" s="47"/>
+      <c r="B54" s="48"/>
+      <c r="C54" s="49"/>
+      <c r="D54" s="65"/>
+      <c r="E54" s="65"/>
+      <c r="F54" s="58"/>
+      <c r="G54" s="58"/>
       <c r="H54" s="25"/>
     </row>
     <row r="55" spans="1:8" ht="9" customHeight="1">
-      <c r="A55" s="49"/>
-      <c r="B55" s="50"/>
-      <c r="C55" s="51"/>
-      <c r="D55" s="67"/>
-      <c r="E55" s="67"/>
-      <c r="F55" s="93"/>
-      <c r="G55" s="93"/>
+      <c r="A55" s="47"/>
+      <c r="B55" s="48"/>
+      <c r="C55" s="49"/>
+      <c r="D55" s="65"/>
+      <c r="E55" s="65"/>
+      <c r="F55" s="58"/>
+      <c r="G55" s="58"/>
       <c r="H55" s="25"/>
     </row>
     <row r="56" spans="1:8" ht="9" customHeight="1">
-      <c r="A56" s="49"/>
-      <c r="B56" s="50"/>
-      <c r="C56" s="51"/>
-      <c r="D56" s="67"/>
-      <c r="E56" s="67"/>
-      <c r="F56" s="93"/>
-      <c r="G56" s="93"/>
+      <c r="A56" s="47"/>
+      <c r="B56" s="48"/>
+      <c r="C56" s="49"/>
+      <c r="D56" s="65"/>
+      <c r="E56" s="65"/>
+      <c r="F56" s="58"/>
+      <c r="G56" s="58"/>
       <c r="H56" s="25"/>
     </row>
     <row r="57" spans="1:8" ht="9" customHeight="1">
-      <c r="A57" s="49"/>
-      <c r="B57" s="50"/>
-      <c r="C57" s="51"/>
-      <c r="D57" s="58" t="s">
+      <c r="A57" s="47"/>
+      <c r="B57" s="48"/>
+      <c r="C57" s="49"/>
+      <c r="D57" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="E57" s="59"/>
-      <c r="F57" s="60"/>
+      <c r="E57" s="56"/>
+      <c r="F57" s="57"/>
       <c r="G57" s="31"/>
       <c r="H57" s="32"/>
     </row>
     <row r="58" spans="1:8" ht="9" customHeight="1">
-      <c r="A58" s="49"/>
-      <c r="B58" s="50"/>
-      <c r="C58" s="51"/>
+      <c r="A58" s="47"/>
+      <c r="B58" s="48"/>
+      <c r="C58" s="49"/>
       <c r="D58" s="35" t="s">
         <v>48</v>
       </c>
@@ -2060,23 +2081,23 @@
       <c r="H58" s="34"/>
     </row>
     <row r="59" spans="1:8" ht="9" customHeight="1">
-      <c r="A59" s="49"/>
-      <c r="B59" s="50"/>
-      <c r="C59" s="51"/>
-      <c r="D59" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="E59" s="39"/>
-      <c r="F59" s="40"/>
+      <c r="A59" s="47"/>
+      <c r="B59" s="48"/>
+      <c r="C59" s="49"/>
+      <c r="D59" s="92" t="s">
+        <v>59</v>
+      </c>
+      <c r="E59" s="92"/>
+      <c r="F59" s="92"/>
       <c r="G59" s="31"/>
       <c r="H59" s="32"/>
     </row>
     <row r="60" spans="1:8" ht="9" customHeight="1">
-      <c r="A60" s="49"/>
-      <c r="B60" s="50"/>
-      <c r="C60" s="51"/>
+      <c r="A60" s="47"/>
+      <c r="B60" s="48"/>
+      <c r="C60" s="49"/>
       <c r="D60" s="35" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E60" s="36"/>
       <c r="F60" s="37"/>
@@ -2084,32 +2105,32 @@
       <c r="H60" s="34"/>
     </row>
     <row r="61" spans="1:8" ht="9" customHeight="1">
-      <c r="A61" s="49"/>
-      <c r="B61" s="50"/>
-      <c r="C61" s="51"/>
-      <c r="D61" s="39" t="s">
-        <v>51</v>
-      </c>
-      <c r="E61" s="39"/>
+      <c r="A61" s="47"/>
+      <c r="B61" s="48"/>
+      <c r="C61" s="49"/>
+      <c r="D61" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="E61" s="40"/>
       <c r="F61" s="40"/>
       <c r="G61" s="31"/>
       <c r="H61" s="32"/>
     </row>
     <row r="62" spans="1:8" ht="9" customHeight="1" thickBot="1">
-      <c r="A62" s="52"/>
-      <c r="B62" s="53"/>
-      <c r="C62" s="54"/>
-      <c r="D62" s="43" t="s">
-        <v>52</v>
-      </c>
-      <c r="E62" s="44"/>
-      <c r="F62" s="45"/>
-      <c r="G62" s="41"/>
-      <c r="H62" s="42"/>
+      <c r="A62" s="50"/>
+      <c r="B62" s="51"/>
+      <c r="C62" s="52"/>
+      <c r="D62" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="E62" s="42"/>
+      <c r="F62" s="43"/>
+      <c r="G62" s="38"/>
+      <c r="H62" s="39"/>
     </row>
     <row r="63" spans="1:8" ht="9" customHeight="1" thickTop="1">
       <c r="F63" s="30" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G63" s="30"/>
       <c r="H63" s="30"/>
@@ -2133,14 +2154,8 @@
     <row r="71" customFormat="1"/>
   </sheetData>
   <mergeCells count="86">
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="D55:E55"/>
     <mergeCell ref="D56:E56"/>
+    <mergeCell ref="D59:F59"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="F6:H6"/>
     <mergeCell ref="A1:B2"/>
@@ -2210,14 +2225,20 @@
     <mergeCell ref="F53:G53"/>
     <mergeCell ref="F54:G54"/>
     <mergeCell ref="F55:G55"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="D55:E55"/>
     <mergeCell ref="F63:H63"/>
     <mergeCell ref="G57:H58"/>
     <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D59:F59"/>
     <mergeCell ref="G59:H60"/>
     <mergeCell ref="D60:F60"/>
+    <mergeCell ref="G61:H62"/>
     <mergeCell ref="D61:F61"/>
-    <mergeCell ref="G61:H62"/>
     <mergeCell ref="D62:F62"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
